--- a/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
+++ b/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
@@ -101,8 +101,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>

--- a/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
+++ b/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>From "Fixture Park", a fully synthetic deal built to exercise the formats. No real property is described.</t>
+          <t>From "505 West". Pricing is illustrative; see the deal summary for the boundary note.</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Fixture Park</t>
+          <t>505 West</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen to sit inside the band a real per-unit sale price occupies; it is not a quote, an off…</t>
+          <t>Illustrative pricing. $180,000 per unit is a round figure chosen inside the band a real per-unit sale price occupies, set so the resulting cap rate sits within 150 basis points …</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>1400 Example Parkway</t>
+          <t>505 W Baseline Rd</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Sample City</t>
+          <t>Tempe</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>AZ</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>85283</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>Example County</t>
+          <t>Maricopa</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Sample City MSA</t>
+          <t>Phoenix</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Street address read from the synthetic marketing package; city/state/ZIP confirmed against the same document.</t>
+          <t>Street address, city, state and ZIP read from the offering memorandum's property pages and corroborated by the per-unit addresses on the rent-roll export.</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Three-story garden, surface parked</t>
+          <t>Garden-style, two-story walk-up</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>334</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>2,019</t>
+          <t>1,981</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>180 units across six plans: 62 one-bedroom (720–795 SF), 78 two-bedroom (1,050–1,140 SF), 26 three-bedroom flats (1,380 SF), 14 three-bedroom townhomes (1,620 SF). Washer/dryer …</t>
+          <t>334 units across ten floor plans: 163 one-bedroom (720 SF), 159 two-bedroom (846-1,006 SF) and 12 three-bedroom (1,282-1,444 SF). Roughly 44% of units carry a renovated interior…</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Delivered 2019; fully stabilized since 2021</t>
+          <t>Delivered 1981; stabilized operations</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>Sample City Residential Holdings LLC</t>
+          <t>Institutional owner-operator (name withheld)</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>On the market</t>
+          <t>Previously marketed; call for offers has passed</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>$215,000 per unit (illustrative)</t>
+          <t>$180,000 per unit (illustrative)</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>$215,000</t>
+          <t>$180,000</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>$2,332,594</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>$1,795</t>
+          <t>$1,388</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>$1,835</t>
+          <t>$1,284</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>$39,600,000</t>
+          <t>MISSING</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>214.8%</t>
+          <t>963.8%</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>Rate as billed, 2.148 per $100 of assessed value, read from the synthetic county bill for the 2025 tax year.</t>
+          <t>2025 published Maricopa County rate for tax area code 031600, 9.6382 per $100 of assessed value, applied to the limited property value at Arizona's 15% commercial assessment rat…</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>$23,000,000</t>
+          <t>$17,450,000</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>Example Creek Elementary</t>
+          <t>Kyrene de los Ninos Elementary</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>Example Ridge Middle</t>
+          <t>Kyrene Middle School</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>Sample City High</t>
+          <t>Marcos de Niza High School</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>Gross Potential Rent</t>
+          <t>MARKET RENT (1016)</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>A1-101</t>
+          <t>1001</t>
         </is>
       </c>
     </row>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>3X2B</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>1,444.0</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2019-10-25</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G121" s="7" t="inlineStr">
         <is>
-          <t>$1,535</t>
+          <t>$2,150</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="G147" s="7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
-          <t>$1,706</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="G149" s="7" t="inlineStr">
         <is>
-          <t>$1,812</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
-          <t>$1,774</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="G153" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A lease trade-out report exists in the data room but was deliberately excluded from this output set, so there is no basis for a new-versus-renewal trade-out block. The new-lease…</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="G155" s="7" t="inlineStr">
         <is>
-          <t>Alderwood Crossing</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="G157" s="7" t="inlineStr">
         <is>
-          <t>1BR-A</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="G159" s="7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="G161" s="7" t="inlineStr">
         <is>
-          <t>$1,495</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
-          <t>$45</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="G163" s="7" t="inlineStr">
         <is>
-          <t>$1,450</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="G165" s="7" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="G166" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="G167" s="7" t="inlineStr">
         <is>
-          <t>own weekly scrape</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="G172" s="7" t="inlineStr">
         <is>
-          <t>1 mi</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="G173" s="7" t="inlineStr">
         <is>
-          <t>9,840</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="G174" s="7" t="inlineStr">
         <is>
-          <t>4,020</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="G175" s="7" t="inlineStr">
         <is>
-          <t>$78,400</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="G176" s="7" t="inlineStr">
         <is>
-          <t>3,150</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G178" s="7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="G182" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="G183" s="7" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
+++ b/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>From "505 West". Pricing is illustrative; see the deal summary for the boundary note.</t>
+          <t>From "Fixture Park", a fully synthetic deal built to exercise the formats. No real property is described.</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>505 West</t>
+          <t>Fixture Park</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Illustrative pricing. $180,000 per unit is a round figure chosen inside the band a real per-unit sale price occupies, set so the resulting cap rate sits within 150 basis points …</t>
+          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen to sit inside the band a real per-unit sale price occupies; it is not a quote, an off…</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>505 W Baseline Rd</t>
+          <t>1400 Example Parkway</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Tempe</t>
+          <t>Sample City</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TX</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>85283</t>
+          <t>75000</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>Maricopa</t>
+          <t>Example County</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Sample City MSA</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Street address, city, state and ZIP read from the offering memorandum's property pages and corroborated by the per-unit addresses on the rent-roll export.</t>
+          <t>Street address read from the synthetic marketing package; city/state/ZIP confirmed against the same document.</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Garden-style, two-story walk-up</t>
+          <t>Three-story garden, surface parked</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>1,981</t>
+          <t>2,019</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>334 units across ten floor plans: 163 one-bedroom (720 SF), 159 two-bedroom (846-1,006 SF) and 12 three-bedroom (1,282-1,444 SF). Roughly 44% of units carry a renovated interior…</t>
+          <t>180 units across six plans: 62 one-bedroom (720–795 SF), 78 two-bedroom (1,050–1,140 SF), 26 three-bedroom flats (1,380 SF), 14 three-bedroom townhomes (1,620 SF). Washer/dryer …</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Delivered 1981; stabilized operations</t>
+          <t>Delivered 2019; fully stabilized since 2021</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>Institutional owner-operator (name withheld)</t>
+          <t>Sample City Residential Holdings LLC</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>Previously marketed; call for offers has passed</t>
+          <t>On the market</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>$180,000 per unit (illustrative)</t>
+          <t>$215,000 per unit (illustrative)</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>$180,000</t>
+          <t>$215,000</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$2,332,594</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>$1,388</t>
+          <t>$1,795</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>$1,284</t>
+          <t>$1,835</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>$39,600,000</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>963.8%</t>
+          <t>214.8%</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>2025 published Maricopa County rate for tax area code 031600, 9.6382 per $100 of assessed value, applied to the limited property value at Arizona's 15% commercial assessment rat…</t>
+          <t>Rate as billed, 2.148 per $100 of assessed value, read from the synthetic county bill for the 2025 tax year.</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>$17,450,000</t>
+          <t>$23,000,000</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>Kyrene de los Ninos Elementary</t>
+          <t>Example Creek Elementary</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>Kyrene Middle School</t>
+          <t>Example Ridge Middle</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>Marcos de Niza High School</t>
+          <t>Sample City High</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>MARKET RENT (1016)</t>
+          <t>Gross Potential Rent</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>A1-101</t>
         </is>
       </c>
     </row>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>3X2B</t>
+          <t>A1</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>1,444.0</t>
+          <t>720</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2025-07-03</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>2019-10-25</t>
+          <t>2025-07-03</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G121" s="7" t="inlineStr">
         <is>
-          <t>$2,150</t>
+          <t>$1,535</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="G147" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$1,706</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="G149" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$1,812</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$1,774</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="G153" s="7" t="inlineStr">
         <is>
-          <t>A lease trade-out report exists in the data room but was deliberately excluded from this output set, so there is no basis for a new-versus-renewal trade-out block. The new-lease…</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="G155" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Alderwood Crossing</t>
         </is>
       </c>
     </row>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7</t>
         </is>
       </c>
     </row>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="G157" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1BR-A</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="G159" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>735</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="G161" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$1,495</t>
         </is>
       </c>
     </row>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$45</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="G163" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$1,450</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="G165" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>94.0%</t>
         </is>
       </c>
     </row>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="G166" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="G167" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>own weekly scrape</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="G172" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 mi</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="G173" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,840</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="G174" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4,020</t>
         </is>
       </c>
     </row>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="G175" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$78,400</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="G176" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,150</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.1%</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G178" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44.0%</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="G182" s="7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="G183" s="7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>220</t>
         </is>
       </c>
     </row>

--- a/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
+++ b/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Model-Ready Outputs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Audit Trail" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,6 +46,16 @@
       <name val="Calibri"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -64,7 +75,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -86,11 +97,16 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="00808080"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -105,6 +121,14 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6637,4 +6661,1427 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Audit trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Fixture Park — as of 2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>The whole trail, every stamped value. Every value below names the document it came from and where in it. A derived value names the values it was built from — one that could not would not have passed validation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="9" t="n"/>
+      <c r="H4" s="9" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Stamped values in this workbook</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Coverage of the required set</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>42/42 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Source document</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Where in it</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Built from</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Supporting quote / note</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>closing_costs.mortgage_tax.amount</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Vendored state rate table</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>closing_costs.py</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>pricing.price_per_unit, summary.state</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>closing_costs.transfer_tax.amount</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Vendored state rate table</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>closing_costs.py</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>pricing.price_per_unit, summary.state</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>comps.rows</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic weekly rent scrape</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Own weekly scrape; asking and net effective stated separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>demand.rings</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic public data extract</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Ring demographics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>pricing.price_per_unit</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Supplied by the operator</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Illustrative. Inside the band a per-unit sale price occupies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>pricing.unit_count</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic rent roll export</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Rent Roll!A:A</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>summary.unit_count</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>rent_roll.as_of</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic rent roll export</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Rent Roll!A2</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="12" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>rent_roll.lookback_months</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Supplied by the operator</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Analysis knob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>rent_roll.new_tenant_tolerance_days</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Supplied by the operator</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Analysis knob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic rent roll export</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Rent Roll!A4:K183</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Unit identifiers only; the source's resident-name column is never read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>summary.assessed_value_basis</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic county tax record</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Valuation notice</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="12" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>summary.assessment_ratio</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic county tax record</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Rate table</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="12" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>summary.city</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic offering memorandum</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>p.4</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="12" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>summary.construction_status</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic offering memorandum</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>p.6</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="12" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>summary.county</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic offering memorandum</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>p.4</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="12" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>summary.deal_name</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic offering memorandum</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>p.1</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Fixture Park</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>summary.deal_status</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic offering memorandum</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>p.2</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="12" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>summary.delivery_date</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic offering memorandum</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>p.6</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="12" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>summary.fair_market_value</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Supplied by the operator</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Operator's own estimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>summary.in_place_rent_avg</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Unit Mix Summary!H</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Occupied units, weighted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>summary.listing_brokerage</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>summary.seller_entity</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Generic label; no firm or individual is named in a published file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>summary.market_rent_for_model</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Unit Mix Summary!K</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>New-lease average where a plan has new leases in the window, else in-place. Never a blend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>summary.msa</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>summary.city, summary.state</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Metro assigned from the city/state pair.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>summary.pricing_guidance</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Supplied by the operator</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>Illustrative figure supplied directly; not a quote or an offer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>summary.product_detail</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic offering memorandum</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>p.7</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="12" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>summary.product_type</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic offering memorandum</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>p.6</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="12" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>summary.school_elementary_name</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic public data extract</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>School attendance lookup</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="n"/>
+      <c r="F35" s="12" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>summary.school_high_name</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic public data extract</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>School attendance lookup</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="n"/>
+      <c r="F36" s="12" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>summary.school_middle_name</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic public data extract</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>School attendance lookup</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="n"/>
+      <c r="F37" s="12" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>summary.seller_entity</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic offering memorandum</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>p.2</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="12" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>summary.state</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic offering memorandum</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>p.4</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="12" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>summary.street_address</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic offering memorandum</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>p.4</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="n"/>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>1400 Example Parkway</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>summary.structure</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic offering memorandum</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>p.6</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="n"/>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>Three-story garden, surface parked</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>summary.tax_area_code</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic county tax record</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Rate table</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="12" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>summary.tax_basis_label</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic county tax record</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Valuation notice</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="n"/>
+      <c r="F43" s="12" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>summary.tax_basis_note</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic county tax record</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Valuation notice</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="n"/>
+      <c r="F44" s="12" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>summary.tax_billed_amount</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic county tax record</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Tax bill</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="n"/>
+      <c r="F45" s="12" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>summary.tax_billed_year</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic county tax record</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Tax bill</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="n"/>
+      <c r="F46" s="12" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>summary.tax_divisor</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic county tax record</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Rate table</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="n"/>
+      <c r="F47" s="12" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>summary.tax_exemption</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic county tax record</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Valuation notice</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="n"/>
+      <c r="F48" s="12" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>summary.tax_parcel_id</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic county tax record</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Parcel record</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="n"/>
+      <c r="F49" s="12" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>summary.tax_rate_as_billed</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic county tax record</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Rate table, synthetic district</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="n"/>
+      <c r="F50" s="12" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>summary.unit_count</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic rent roll export</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Rent Roll!A:A</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Distinct unit identifiers on the roll.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>summary.year_built</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic offering memorandum</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>p.6</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="n"/>
+      <c r="F52" s="12" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>summary.zip</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic offering memorandum</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>p.4</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="n"/>
+      <c r="F53" s="12" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>supply.rings</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic public data extract</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="n"/>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Permit and entitlement records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>t12.month_labels</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic trailing-twelve income statement</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>T-12!C8:N8</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="n"/>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Twelve consecutive month-end columns; direction detected from the labels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>t12.source_subtotals</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic trailing-twelve income statement</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>T-12!O</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="n"/>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>The statement's own printed subtotals, kept for the cross-tie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>t12.units</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic rent roll export</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>summary.unit_count</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>trade_out.rows</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic lease trade-out report</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="n"/>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>Cohort averages.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
+++ b/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
@@ -125,10 +125,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G185"/>
+  <dimension ref="A1:G201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7">
@@ -2231,32 +2231,32 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>computed_annual_tax</t>
+          <t>tax_parcel_id</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Basis times ratio over divisor times rate, less exemption.</t>
+          <t>Assessor parcel number the bill is issued against. A tax figure that cannot name its parcel cannot be checked.</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>County tax portal</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Property tax expense</t>
+          <t>Tax evidence</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SYN-000-00-000</t>
         </is>
       </c>
     </row>
@@ -2268,57 +2268,81 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>computed_tax_per_unit</t>
+          <t>tax_area_code</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Computed annual tax divided by unit count.</t>
+          <t>Tax area / district code, which selects the published rate row that applies.</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>County tax portal</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>Property tax per unit</t>
+          <t>Tax evidence</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SYN-0000</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="n"/>
-      <c r="C61" s="5" t="n"/>
-      <c r="D61" s="5" t="n"/>
-      <c r="E61" s="5" t="n"/>
-      <c r="F61" s="5" t="n"/>
-      <c r="G61" s="5" t="n"/>
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>tax_basis_label</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>What the assessed basis IS in that state — a limited value, a market value, an appraised value. The word matters because only some of them reset on sale.</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>County tax portal</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Tax inputs</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>Assessed value (synthetic)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>Schools</t>
+          <t>Taxes</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>school_elementary_name</t>
+          <t>tax_basis_note</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
@@ -2328,232 +2352,232 @@
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>Zoned elementary school.</t>
+          <t>How that basis behaves on a sale. Where a state caps growth and does not reset on transfer, pricing tax off the purchase price overstates it badly.</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Public school-rating source</t>
+          <t>County tax portal</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Tax inputs</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>Example Creek Elementary</t>
+          <t>Synthetic basis. On a real deal this row states what the basis IS in that state and whether it resets on sale.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>Schools</t>
+          <t>Taxes</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>school_elementary_rating</t>
+          <t>tax_billed_amount</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Elementary rating on a 1–10 scale.</t>
+          <t>The tax the county actually billed, for the year stated — the figure the computed tax is checked against.</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>Public school-rating source</t>
+          <t>County tax portal</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Tax evidence</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>$494,040</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>Schools</t>
+          <t>Taxes</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>school_middle_name</t>
+          <t>tax_billed_year</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Zoned middle school.</t>
+          <t>Tax year of the billed figure.</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Public school-rating source</t>
+          <t>County tax portal</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Tax evidence</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>Example Ridge Middle</t>
+          <t>2,025</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>Schools</t>
+          <t>Taxes</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>school_middle_rating</t>
+          <t>computed_annual_tax</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Middle-school rating on a 1–10 scale.</t>
+          <t>Basis times ratio over divisor times rate, less exemption.</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Public school-rating source</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Property tax expense</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>Schools</t>
+          <t>Taxes</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>school_high_name</t>
+          <t>computed_tax_per_unit</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Computed annual tax divided by unit count.</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>Property tax per unit</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Closing costs</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n"/>
+      <c r="C67" s="5" t="n"/>
+      <c r="D67" s="5" t="n"/>
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="5" t="n"/>
+      <c r="G67" s="5" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Closing costs</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>closing_state</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Zoned high school.</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>Public school-rating source</t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>Reference only — not a model input</t>
-        </is>
-      </c>
-      <c r="G66" s="7" t="inlineStr">
-        <is>
-          <t>Sample City High</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>school_high_rating</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>High-school rating on a 1–10 scale.</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>Public school-rating source</t>
-        </is>
-      </c>
-      <c r="F67" s="7" t="inlineStr">
-        <is>
-          <t>Reference only — not a model input</t>
-        </is>
-      </c>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>T-12 revenue</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="n"/>
-      <c r="C68" s="5" t="n"/>
-      <c r="D68" s="5" t="n"/>
-      <c r="E68" s="5" t="n"/>
-      <c r="F68" s="5" t="n"/>
-      <c r="G68" s="5" t="n"/>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>State whose statutes the closing costs are computed under. Cross-checked against the property's own state.</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>Closing cost assumptions</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>T-12 revenue</t>
+          <t>Closing costs</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Gross Potential Rent</t>
+          <t>closing_price</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
@@ -2563,34 +2587,34 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Gross Potential Rent — trailing-twelve total, and trailing-three annualized beside it.</t>
+          <t>Consideration the transfer tax is computed on: price per unit times unit count.</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Trailing-twelve-month income statement</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>Investment analysis — T-12 revenue column</t>
+          <t>Closing cost assumptions</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$38,700,000</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>T-12 revenue</t>
+          <t>Closing costs</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Gain/(Loss) to Lease</t>
+          <t>loan_amount</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
@@ -2600,17 +2624,17 @@
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Gain/(Loss) to Lease — trailing-twelve total, and trailing-three annualized beside it.</t>
+          <t>Loan the mortgage or recording tax is computed on. Absent, that tax is reported as not asserted rather than inferred from the price.</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Trailing-twelve-month income statement</t>
+          <t>Supplied by the operator</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Investment analysis — T-12 revenue column</t>
+          <t>Debt assumptions</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
@@ -2622,12 +2646,12 @@
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>T-12 revenue</t>
+          <t>Closing costs</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Gross Scheduled Rent</t>
+          <t>transfer_tax_amount</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
@@ -2637,108 +2661,108 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Gross Scheduled Rent — trailing-twelve total, and trailing-three annualized beside it.</t>
+          <t>State or county real-estate transfer tax at the stated price.</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Trailing-twelve-month income statement</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>Investment analysis — T-12 revenue column</t>
+          <t>Closing costs</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>T-12 revenue</t>
+          <t>Closing costs</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Vacancy</t>
+          <t>transfer_tax_rate</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Vacancy — trailing-twelve total, and trailing-three annualized beside it.</t>
+          <t>The rate applied, as the statute expresses it.</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Trailing-twelve-month income statement</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>Investment analysis — T-12 revenue column</t>
+          <t>Closing costs</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No real-estate transfer tax</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>T-12 revenue</t>
+          <t>Closing costs</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Concessions</t>
+          <t>transfer_tax_citation</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Concessions — trailing-twelve total, and trailing-three annualized beside it.</t>
+          <t>Statute or revenue-department authority for the rate — including where the authority is that no such tax exists.</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>Trailing-twelve-month income statement</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Investment analysis — T-12 revenue column</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Tex. Const. art. VIII, sec. 29 (added 2015)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>T-12 revenue</t>
+          <t>Closing costs</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Non-Revenue Units</t>
+          <t>mortgage_tax_amount</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
@@ -2748,380 +2772,356 @@
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>Non-Revenue Units — trailing-twelve total, and trailing-three annualized beside it.</t>
+          <t>Mortgage, intangible or recording tax on the security instrument, computed on the loan.</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Trailing-twelve-month income statement</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>Investment analysis — T-12 revenue column</t>
+          <t>Closing costs</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>T-12 revenue</t>
+          <t>Closing costs</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Delinquency</t>
+          <t>mortgage_tax_rate</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Delinquency — trailing-twelve total, and trailing-three annualized beside it.</t>
+          <t>The rate applied, as the statute expresses it.</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>Trailing-twelve-month income statement</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Investment analysis — T-12 revenue column</t>
+          <t>Closing costs</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No mortgage tax</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>T-12 revenue</t>
+          <t>Closing costs</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Utility Reimbursements</t>
+          <t>mortgage_tax_citation</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Utility Reimbursements — trailing-twelve total, and trailing-three annualized beside it.</t>
+          <t>Statute or revenue-department authority for the rate.</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Trailing-twelve-month income statement</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>Investment analysis — T-12 revenue column</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No imposing statute; Tex. Loc. Gov't Code ch. 118</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>T-12 revenue</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>Other Income</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Other Income — trailing-twelve total, and trailing-three annualized beside it.</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>Trailing-twelve-month income statement</t>
-        </is>
-      </c>
-      <c r="F77" s="7" t="inlineStr">
-        <is>
-          <t>Investment analysis — T-12 revenue column</t>
-        </is>
-      </c>
-      <c r="G77" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Schools</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n"/>
+      <c r="C77" s="5" t="n"/>
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="n"/>
+      <c r="G77" s="5" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>T-12 revenue</t>
+          <t>Schools</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Revenue Adjustments</t>
+          <t>school_elementary_name</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Revenue Adjustments — trailing-twelve total, and trailing-three annualized beside it.</t>
+          <t>Zoned elementary school.</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Trailing-twelve-month income statement</t>
+          <t>Public school-rating source</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>Investment analysis — T-12 revenue column</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Example Creek Elementary</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>T-12 revenue</t>
+          <t>Schools</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Total Revenue</t>
+          <t>school_elementary_rating</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Total Revenue — trailing-twelve total, and trailing-three annualized beside it.</t>
+          <t>Elementary rating on a 1–10 scale.</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>Trailing-twelve-month income statement</t>
+          <t>Public school-rating source</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>Investment analysis — T-12 revenue column</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>T-12 expense</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="n"/>
-      <c r="C80" s="5" t="n"/>
-      <c r="D80" s="5" t="n"/>
-      <c r="E80" s="5" t="n"/>
-      <c r="F80" s="5" t="n"/>
-      <c r="G80" s="5" t="n"/>
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Schools</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>school_middle_name</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Zoned middle school.</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>Public school-rating source</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>Example Ridge Middle</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>T-12 expense</t>
+          <t>Schools</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>G&amp;A</t>
+          <t>school_middle_rating</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>G&amp;A — trailing-twelve total, trailing-three annualized, and per unit.</t>
+          <t>Middle-school rating on a 1–10 scale.</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>Trailing-twelve-month income statement</t>
+          <t>Public school-rating source</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>Investment analysis — T-12 expense column</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>T-12 expense</t>
+          <t>Schools</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Leasing and Marketing</t>
+          <t>school_high_name</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>Leasing and Marketing — trailing-twelve total, trailing-three annualized, and per unit.</t>
+          <t>Zoned high school.</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Trailing-twelve-month income statement</t>
+          <t>Public school-rating source</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>Investment analysis — T-12 expense column</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sample City High</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>T-12 expense</t>
+          <t>Schools</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>school_high_rating</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Payroll — trailing-twelve total, trailing-three annualized, and per unit.</t>
+          <t>High-school rating on a 1–10 scale.</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>Trailing-twelve-month income statement</t>
+          <t>Public school-rating source</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Investment analysis — T-12 expense column</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>T-12 expense</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>Insurance — trailing-twelve total, trailing-three annualized, and per unit.</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>Trailing-twelve-month income statement</t>
-        </is>
-      </c>
-      <c r="F84" s="7" t="inlineStr">
-        <is>
-          <t>Investment analysis — T-12 expense column</t>
-        </is>
-      </c>
-      <c r="G84" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>T-12 revenue</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n"/>
+      <c r="C84" s="5" t="n"/>
+      <c r="D84" s="5" t="n"/>
+      <c r="E84" s="5" t="n"/>
+      <c r="F84" s="5" t="n"/>
+      <c r="G84" s="5" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>T-12 expense</t>
+          <t>T-12 revenue</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Property Taxes</t>
+          <t>Gross Potential Rent</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Property Taxes — trailing-twelve total, trailing-three annualized, and per unit.</t>
+          <t>Gross Potential Rent — trailing-twelve total, and trailing-three annualized beside it.</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>Investment analysis — T-12 expense column</t>
+          <t>Investment analysis — T-12 revenue column</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
@@ -3153,12 +3153,12 @@
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>T-12 expense</t>
+          <t>T-12 revenue</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Legal and Professional</t>
+          <t>Gain/(Loss) to Lease</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Legal and Professional — trailing-twelve total, trailing-three annualized, and per unit.</t>
+          <t>Gain/(Loss) to Lease — trailing-twelve total, and trailing-three annualized beside it.</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>Investment analysis — T-12 expense column</t>
+          <t>Investment analysis — T-12 revenue column</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
@@ -3190,12 +3190,12 @@
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>T-12 expense</t>
+          <t>T-12 revenue</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Management Fee</t>
+          <t>Gross Scheduled Rent</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Management Fee — trailing-twelve total, trailing-three annualized, and per unit.</t>
+          <t>Gross Scheduled Rent — trailing-twelve total, and trailing-three annualized beside it.</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>Investment analysis — T-12 expense column</t>
+          <t>Investment analysis — T-12 revenue column</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
@@ -3227,12 +3227,12 @@
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>T-12 expense</t>
+          <t>T-12 revenue</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Vacancy</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Landscaping — trailing-twelve total, trailing-three annualized, and per unit.</t>
+          <t>Vacancy — trailing-twelve total, and trailing-three annualized beside it.</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>Investment analysis — T-12 expense column</t>
+          <t>Investment analysis — T-12 revenue column</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
@@ -3264,12 +3264,12 @@
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>T-12 expense</t>
+          <t>T-12 revenue</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Repairs and Maintenance</t>
+          <t>Concessions</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Repairs and Maintenance — trailing-twelve total, trailing-three annualized, and per unit.</t>
+          <t>Concessions — trailing-twelve total, and trailing-three annualized beside it.</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>Investment analysis — T-12 expense column</t>
+          <t>Investment analysis — T-12 revenue column</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
@@ -3301,12 +3301,12 @@
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>T-12 expense</t>
+          <t>T-12 revenue</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Unit Turns</t>
+          <t>Non-Revenue Units</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Unit Turns — trailing-twelve total, trailing-three annualized, and per unit.</t>
+          <t>Non-Revenue Units — trailing-twelve total, and trailing-three annualized beside it.</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>Investment analysis — T-12 expense column</t>
+          <t>Investment analysis — T-12 revenue column</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
@@ -3338,12 +3338,12 @@
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>T-12 expense</t>
+          <t>T-12 revenue</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Delinquency</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Utilities — trailing-twelve total, trailing-three annualized, and per unit.</t>
+          <t>Delinquency — trailing-twelve total, and trailing-three annualized beside it.</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>Investment analysis — T-12 expense column</t>
+          <t>Investment analysis — T-12 revenue column</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
@@ -3375,12 +3375,12 @@
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>T-12 expense</t>
+          <t>T-12 revenue</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Expense Adjustments</t>
+          <t>Utility Reimbursements</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>Expense Adjustments — trailing-twelve total, trailing-three annualized, and per unit.</t>
+          <t>Utility Reimbursements — trailing-twelve total, and trailing-three annualized beside it.</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>Investment analysis — T-12 expense column</t>
+          <t>Investment analysis — T-12 revenue column</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
@@ -3410,37 +3410,61 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>T-12 structure</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="n"/>
-      <c r="C93" s="5" t="n"/>
-      <c r="D93" s="5" t="n"/>
-      <c r="E93" s="5" t="n"/>
-      <c r="F93" s="5" t="n"/>
-      <c r="G93" s="5" t="n"/>
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>T-12 revenue</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>Other Income — trailing-twelve total, and trailing-three annualized beside it.</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>Trailing-twelve-month income statement</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>Investment analysis — T-12 revenue column</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>T-12 structure</t>
+          <t>T-12 revenue</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>month_labels</t>
+          <t>Revenue Adjustments</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Twelve month labels in the source statement's own order.</t>
+          <t>Revenue Adjustments — trailing-twelve total, and trailing-three annualized beside it.</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -3450,7 +3474,7 @@
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>T-12 column headers</t>
+          <t>Investment analysis — T-12 revenue column</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
@@ -3462,32 +3486,32 @@
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>T-12 structure</t>
+          <t>T-12 revenue</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>month_order</t>
+          <t>Total Revenue</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Whether the months run oldest-first or newest-first. Detected from the labels, never assumed, because the T-3 window depends on it.</t>
+          <t>Total Revenue — trailing-twelve total, and trailing-three annualized beside it.</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Trailing-twelve-month income statement</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Investment analysis — T-12 revenue column</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
@@ -3497,88 +3521,64 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>T-12 structure</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>line_item_label</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>The source statement's own wording for a line, kept verbatim beside the category it was mapped to.</t>
-        </is>
-      </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>Trailing-twelve-month income statement</t>
-        </is>
-      </c>
-      <c r="F96" s="7" t="inlineStr">
-        <is>
-          <t>T-12 line item</t>
-        </is>
-      </c>
-      <c r="G96" s="7" t="inlineStr">
-        <is>
-          <t>Gross Potential Rent</t>
-        </is>
-      </c>
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>T-12 expense</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n"/>
+      <c r="C96" s="5" t="n"/>
+      <c r="D96" s="5" t="n"/>
+      <c r="E96" s="5" t="n"/>
+      <c r="F96" s="5" t="n"/>
+      <c r="G96" s="5" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>T-12 structure</t>
+          <t>T-12 expense</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>line_item_category</t>
+          <t>G&amp;A</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Which vendored category a source line was mapped to. Blank for an uncategorized subtotal, which stays visible rather than being dropped.</t>
+          <t>G&amp;A — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Trailing-twelve-month income statement</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>T-12 mapping</t>
+          <t>Investment analysis — T-12 expense column</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>Gross Potential Rent</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>T-12 structure</t>
+          <t>T-12 expense</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>line_item_t12_total</t>
+          <t>Leasing and Marketing</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
@@ -3588,17 +3588,17 @@
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Sum of a line's twelve months.</t>
+          <t>Leasing and Marketing — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Trailing-twelve-month income statement</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>T-12 column</t>
+          <t>Investment analysis — T-12 expense column</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
@@ -3610,12 +3610,12 @@
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>T-12 structure</t>
+          <t>T-12 expense</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>line_item_t3_total</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
@@ -3625,17 +3625,17 @@
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Sum of a line's three most recent months, taken from whichever end the direction detector found.</t>
+          <t>Payroll — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Trailing-twelve-month income statement</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>T-3 column</t>
+          <t>Investment analysis — T-12 expense column</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
@@ -3647,12 +3647,12 @@
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>T-12 structure</t>
+          <t>T-12 expense</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>gross_scheduled_rent</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
@@ -3662,17 +3662,17 @@
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>Printed on the statement where it exists, otherwise gross potential rent plus gain/(loss) to lease. Which one fired is visible in the workbook formula.</t>
+          <t>Insurance — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Trailing-twelve-month income statement</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Gross scheduled rent</t>
+          <t>Investment analysis — T-12 expense column</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
@@ -3684,12 +3684,12 @@
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>T-12 structure</t>
+          <t>T-12 expense</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>total_revenue</t>
+          <t>Property Taxes</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -3699,17 +3699,17 @@
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Sum from gross scheduled rent down through revenue adjustments — never from gross potential rent, which double-counts loss-to-lease.</t>
+          <t>Property Taxes — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Trailing-twelve-month income statement</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Total revenue</t>
+          <t>Investment analysis — T-12 expense column</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
@@ -3721,12 +3721,12 @@
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>T-12 structure</t>
+          <t>T-12 expense</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>total_operating_expenses</t>
+          <t>Legal and Professional</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
@@ -3736,17 +3736,17 @@
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Sum of the twelve expense categories.</t>
+          <t>Legal and Professional — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Trailing-twelve-month income statement</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>Total operating expenses</t>
+          <t>Investment analysis — T-12 expense column</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
@@ -3758,12 +3758,12 @@
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>T-12 structure</t>
+          <t>T-12 expense</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>net_operating_income</t>
+          <t>Management Fee</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
@@ -3773,17 +3773,17 @@
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Total revenue less total operating expenses.</t>
+          <t>Management Fee — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Trailing-twelve-month income statement</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>Net operating income</t>
+          <t>Investment analysis — T-12 expense column</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
@@ -3795,12 +3795,12 @@
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>T-12 structure</t>
+          <t>T-12 expense</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>t3_annualized</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
@@ -3810,17 +3810,17 @@
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Trailing-three total times four, beside every rollup row.</t>
+          <t>Landscaping — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Trailing-twelve-month income statement</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>T-3 annualized column</t>
+          <t>Investment analysis — T-12 expense column</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
@@ -3832,12 +3832,12 @@
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>T-12 structure</t>
+          <t>T-12 expense</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>t6_annualized</t>
+          <t>Repairs and Maintenance</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
@@ -3847,17 +3847,17 @@
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Trailing-six total times two, so a reader can see whether the trend is up or down.</t>
+          <t>Repairs and Maintenance — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Trailing-twelve-month income statement</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>Trend cross-check</t>
+          <t>Investment analysis — T-12 expense column</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
@@ -3869,12 +3869,12 @@
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>T-12 structure</t>
+          <t>T-12 expense</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>expense_per_unit</t>
+          <t>Unit Turns</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
@@ -3884,17 +3884,17 @@
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>Each rollup row divided by unit count, blank-guarded so a bad unit count cannot fill the column with errors.</t>
+          <t>Unit Turns — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Trailing-twelve-month income statement</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>Per-unit expense check</t>
+          <t>Investment analysis — T-12 expense column</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
@@ -3906,32 +3906,32 @@
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>T-12 structure</t>
+          <t>T-12 expense</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>pct_of_revenue</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Each rollup row as a share of total revenue.</t>
+          <t>Utilities — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Trailing-twelve-month income statement</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>Expense ratio check</t>
+          <t>Investment analysis — T-12 expense column</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
@@ -3943,76 +3943,52 @@
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
+          <t>T-12 expense</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>Expense Adjustments</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>Expense Adjustments — trailing-twelve total, trailing-three annualized, and per unit.</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>Trailing-twelve-month income statement</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>Investment analysis — T-12 expense column</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
           <t>T-12 structure</t>
         </is>
       </c>
-      <c r="B108" s="6" t="inlineStr">
-        <is>
-          <t>breakout_top4</t>
-        </is>
-      </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>table</t>
-        </is>
-      </c>
-      <c r="D108" s="7" t="inlineStr">
-        <is>
-          <t>For other income, utility reimbursements, and utilities: the four largest constituent lines plus a Rest row, tying to the rollup.</t>
-        </is>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F108" s="7" t="inlineStr">
-        <is>
-          <t>Other-income / utility detail</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>T-12 structure</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>source_subtotal</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D109" s="7" t="inlineStr">
-        <is>
-          <t>A subtotal as printed on the source statement, kept for the cross-tie.</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>Trailing-twelve-month income statement</t>
-        </is>
-      </c>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>Reference only — not a model input</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B109" s="5" t="n"/>
+      <c r="C109" s="5" t="n"/>
+      <c r="D109" s="5" t="n"/>
+      <c r="E109" s="5" t="n"/>
+      <c r="F109" s="5" t="n"/>
+      <c r="G109" s="5" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
@@ -4022,57 +3998,81 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>error_check_difference</t>
+          <t>month_labels</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>Our category total less the source's printed subtotal. Anything over a dollar reads REVIEW rather than quietly passing.</t>
+          <t>Twelve month labels in the source statement's own order.</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
+          <t>Trailing-twelve-month income statement</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>T-12 column headers</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>T-12 structure</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>month_order</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>Whether the months run oldest-first or newest-first. Detected from the labels, never assumed, because the T-3 window depends on it.</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="F110" s="7" t="inlineStr">
+      <c r="F111" s="7" t="inlineStr">
         <is>
           <t>Reference only — not a model input</t>
         </is>
       </c>
-      <c r="G110" s="7" t="inlineStr">
+      <c r="G111" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>Rent roll — unit</t>
-        </is>
-      </c>
-      <c r="B111" s="5" t="n"/>
-      <c r="C111" s="5" t="n"/>
-      <c r="D111" s="5" t="n"/>
-      <c r="E111" s="5" t="n"/>
-      <c r="F111" s="5" t="n"/>
-      <c r="G111" s="5" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — unit</t>
+          <t>T-12 structure</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>unit_id</t>
+          <t>line_item_label</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
@@ -4082,34 +4082,34 @@
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>Unit identifier. The output carries unit IDs only; no tenant-name column exists in the schema.</t>
+          <t>The source statement's own wording for a line, kept verbatim beside the category it was mapped to.</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>Rent roll export</t>
+          <t>Trailing-twelve-month income statement</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>Unit list</t>
+          <t>T-12 line item</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>A1-101</t>
+          <t>Gross Potential Rent</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — unit</t>
+          <t>T-12 structure</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>floor_plan</t>
+          <t>line_item_category</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
@@ -4119,266 +4119,266 @@
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Floor-plan code the unit belongs to.</t>
+          <t>Which vendored category a source line was mapped to. Blank for an uncategorized subtotal, which stays visible rather than being dropped.</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>Rent roll export</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Unit mix</t>
+          <t>T-12 mapping</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>Gross Potential Rent</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — unit</t>
+          <t>T-12 structure</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>beds</t>
+          <t>line_item_t12_total</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>Bedrooms.</t>
+          <t>Sum of a line's twelve months.</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>Rent roll export</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>Unit mix</t>
+          <t>T-12 column</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — unit</t>
+          <t>T-12 structure</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>baths</t>
+          <t>line_item_t3_total</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>Bathrooms.</t>
+          <t>Sum of a line's three most recent months, taken from whichever end the direction detector found.</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>Rent roll export</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Unit mix</t>
+          <t>T-3 column</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — unit</t>
+          <t>T-12 structure</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>sqft</t>
+          <t>gross_scheduled_rent</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>Square footage.</t>
+          <t>Printed on the statement where it exists, otherwise gross potential rent plus gain/(loss) to lease. Which one fired is visible in the workbook formula.</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>Rent roll export</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>Unit mix</t>
+          <t>Gross scheduled rent</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — unit</t>
+          <t>T-12 structure</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>total_revenue</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>Occupied, vacant, or model/down.</t>
+          <t>Sum from gross scheduled rent down through revenue adjustments — never from gross potential rent, which double-counts loss-to-lease.</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>Rent roll export</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Total revenue</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr">
         <is>
-          <t>Occupied</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — unit</t>
+          <t>T-12 structure</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>lease_start</t>
+          <t>total_operating_expenses</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>Lease start. A value the source gave as text stays text — a date that arrives as 'n/a' is not coerced into 1899.</t>
+          <t>Sum of the twelve expense categories.</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>Rent roll export</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Total operating expenses</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — unit</t>
+          <t>T-12 structure</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>move_in</t>
+          <t>net_operating_income</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>Move-in date. Turnover is counted by move-in, not by lease start.</t>
+          <t>Total revenue less total operating expenses.</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>Rent roll export</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Turnover</t>
+          <t>Net operating income</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — unit</t>
+          <t>T-12 structure</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>lease_type</t>
+          <t>t3_annualized</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>New, Renewal, or blank. Blank means the source could not support a classification — never a guess, never a blend.</t>
+          <t>Trailing-three total times four, beside every rollup row.</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -4388,24 +4388,24 @@
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>New-vs-renewal split</t>
+          <t>T-3 annualized column</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — unit</t>
+          <t>T-12 structure</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>in_place_rent</t>
+          <t>t6_annualized</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
@@ -4415,34 +4415,34 @@
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>Contract rent in place.</t>
+          <t>Trailing-six total times two, so a reader can see whether the trend is up or down.</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>Rent roll export</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>In-place rent</t>
+          <t>Trend cross-check</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr">
         <is>
-          <t>$1,535</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — unit</t>
+          <t>T-12 structure</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>rent_per_sf</t>
+          <t>expense_per_unit</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>In-place rent divided by square footage.</t>
+          <t>Each rollup row divided by unit count, blank-guarded so a bad unit count cannot fill the column with errors.</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>Rent per square foot</t>
+          <t>Per-unit expense check</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
@@ -4472,37 +4472,61 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>Rent roll — plan</t>
-        </is>
-      </c>
-      <c r="B123" s="5" t="n"/>
-      <c r="C123" s="5" t="n"/>
-      <c r="D123" s="5" t="n"/>
-      <c r="E123" s="5" t="n"/>
-      <c r="F123" s="5" t="n"/>
-      <c r="G123" s="5" t="n"/>
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>T-12 structure</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>pct_of_revenue</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>Each rollup row as a share of total revenue.</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t>Expense ratio check</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — plan</t>
+          <t>T-12 structure</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>plan_avg_sqft</t>
+          <t>breakout_top4</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>table</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>Average square footage for the plan.</t>
+          <t>For other income, utility reimbursements, and utilities: the four largest constituent lines plus a Rest row, tying to the rollup.</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -4512,7 +4536,7 @@
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>Unit mix — average SF</t>
+          <t>Other-income / utility detail</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
@@ -4524,32 +4548,32 @@
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — plan</t>
+          <t>T-12 structure</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>plan_units</t>
+          <t>source_subtotal</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>Units in the plan.</t>
+          <t>A subtotal as printed on the source statement, kept for the cross-tie.</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Trailing-twelve-month income statement</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Unit mix — count</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
@@ -4561,22 +4585,22 @@
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — plan</t>
+          <t>T-12 structure</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>plan_occupied</t>
+          <t>error_check_difference</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>Occupied units in the plan.</t>
+          <t>Our category total less the source's printed subtotal. Anything over a dollar reads REVIEW rather than quietly passing.</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -4586,7 +4610,7 @@
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>Occupancy by plan</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
@@ -4596,333 +4620,333 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>Rent roll — plan</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>plan_vacant</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D127" s="7" t="inlineStr">
-        <is>
-          <t>Vacant units in the plan.</t>
-        </is>
-      </c>
-      <c r="E127" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F127" s="7" t="inlineStr">
-        <is>
-          <t>Occupancy by plan</t>
-        </is>
-      </c>
-      <c r="G127" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>Rent roll — unit</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="n"/>
+      <c r="C127" s="5" t="n"/>
+      <c r="D127" s="5" t="n"/>
+      <c r="E127" s="5" t="n"/>
+      <c r="F127" s="5" t="n"/>
+      <c r="G127" s="5" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — plan</t>
+          <t>Rent roll — unit</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>plan_avg_in_place_rent</t>
+          <t>unit_id</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>Weighted average in-place rent for the plan's occupied units.</t>
+          <t>Unit identifier. The output carries unit IDs only; no tenant-name column exists in the schema.</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Rent roll export</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>In-place rent by plan</t>
+          <t>Unit list</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A1-101</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — plan</t>
+          <t>Rent roll — unit</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>plan_new_lease_rent</t>
+          <t>floor_plan</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>Average rent on the plan's new leases inside the lookback window. Renewals are excluded.</t>
+          <t>Floor-plan code the unit belongs to.</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Rent roll export</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>New-lease rent evidence</t>
+          <t>Unit mix</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A1</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — plan</t>
+          <t>Rent roll — unit</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>plan_new_lease_count</t>
+          <t>beds</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>How many new leases the average rests on. A thin count is visible rather than implied.</t>
+          <t>Bedrooms.</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Rent roll export</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>Sample size</t>
+          <t>Unit mix</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — plan</t>
+          <t>Rent roll — unit</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>plan_market_rent_for_model</t>
+          <t>baths</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>The plan's rent to underwrite: new-lease average where one exists, otherwise in-place. This is the column a financial model consumes.</t>
+          <t>Bathrooms.</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Rent roll export</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>Unit-mix market rent</t>
+          <t>Unit mix</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — plan</t>
+          <t>Rent roll — unit</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>plan_market_rent_basis</t>
+          <t>sqft</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>Square footage.</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll export</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>Unit mix</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll — unit</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D132" s="7" t="inlineStr">
-        <is>
-          <t>Which of the two fired, stated per plan.</t>
-        </is>
-      </c>
-      <c r="E132" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F132" s="7" t="inlineStr">
-        <is>
-          <t>Reference only — not a model input</t>
-        </is>
-      </c>
-      <c r="G132" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>Rent roll — totals</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="n"/>
-      <c r="C133" s="5" t="n"/>
-      <c r="D133" s="5" t="n"/>
-      <c r="E133" s="5" t="n"/>
-      <c r="F133" s="5" t="n"/>
-      <c r="G133" s="5" t="n"/>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>Occupied, vacant, or model/down.</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll export</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — totals</t>
+          <t>Rent roll — unit</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>total_units</t>
+          <t>lease_start</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>Units on the roll.</t>
+          <t>Lease start. A value the source gave as text stays text — a date that arrives as 'n/a' is not coerced into 1899.</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Rent roll export</t>
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>Unit count cross-check</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2025-07-03</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — totals</t>
+          <t>Rent roll — unit</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>occupied_units</t>
+          <t>move_in</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Occupied units.</t>
+          <t>Move-in date. Turnover is counted by move-in, not by lease start.</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Rent roll export</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Turnover</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2025-07-03</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — totals</t>
+          <t>Rent roll — unit</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>vacant_units</t>
+          <t>lease_type</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>Vacant units.</t>
+          <t>New, Renewal, or blank. Blank means the source could not support a classification — never a guess, never a blend.</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -4932,71 +4956,71 @@
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>New-vs-renewal split</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — totals</t>
+          <t>Rent roll — unit</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>occupancy</t>
+          <t>in_place_rent</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>Occupied over total.</t>
+          <t>Contract rent in place.</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Rent roll export</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>Vacancy assumption</t>
+          <t>In-place rent</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$1,535</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — totals</t>
+          <t>Rent roll — unit</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>vacancy</t>
+          <t>rent_per_sf</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>One less occupancy. The physical-vacancy input.</t>
+          <t>In-place rent divided by square footage.</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -5006,7 +5030,7 @@
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>Vacancy assumption</t>
+          <t>Rent per square foot</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
@@ -5016,61 +5040,37 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="6" t="inlineStr">
-        <is>
-          <t>Rent roll — totals</t>
-        </is>
-      </c>
-      <c r="B139" s="6" t="inlineStr">
-        <is>
-          <t>wavg_in_place_rent</t>
-        </is>
-      </c>
-      <c r="C139" s="6" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D139" s="7" t="inlineStr">
-        <is>
-          <t>Unit-weighted in-place rent across the property.</t>
-        </is>
-      </c>
-      <c r="E139" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F139" s="7" t="inlineStr">
-        <is>
-          <t>In-place rent</t>
-        </is>
-      </c>
-      <c r="G139" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>Rent roll — plan</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="n"/>
+      <c r="C139" s="5" t="n"/>
+      <c r="D139" s="5" t="n"/>
+      <c r="E139" s="5" t="n"/>
+      <c r="F139" s="5" t="n"/>
+      <c r="G139" s="5" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — totals</t>
+          <t>Rent roll — plan</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>wavg_market_rent_for_model</t>
+          <t>plan_avg_sqft</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>Unit-weighted market rent for model across the property.</t>
+          <t>Average square footage for the plan.</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>Market rent</t>
+          <t>Unit mix — average SF</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr">
@@ -5092,22 +5092,22 @@
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — totals</t>
+          <t>Rent roll — plan</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>annualized_turnover</t>
+          <t>plan_units</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>Move-ins inside the lookback window, annualized against unit count.</t>
+          <t>Units in the plan.</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>Turnover assumption</t>
+          <t>Unit mix — count</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr">
@@ -5129,12 +5129,12 @@
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — totals</t>
+          <t>Rent roll — plan</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>lookback_months</t>
+          <t>plan_occupied</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
@@ -5144,34 +5144,34 @@
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>Length of the new-lease window, measured back from the roll's as-of date.</t>
+          <t>Occupied units in the plan.</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Occupancy by plan</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — totals</t>
+          <t>Rent roll — plan</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>new_tenant_tolerance_days</t>
+          <t>plan_vacant</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
@@ -5181,279 +5181,279 @@
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>How far lease start may sit from move-in before a lease stops counting as a new tenant. A knob on the output, not a constant buried in code.</t>
+          <t>Vacant units in the plan.</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Occupancy by plan</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>Rent roll — totals</t>
+          <t>Rent roll — plan</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>roll_as_of</t>
+          <t>plan_avg_in_place_rent</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>As-of date of the roll. Every window is measured from here.</t>
+          <t>Weighted average in-place rent for the plan's occupied units.</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>Rent roll export</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>Analysis date</t>
+          <t>In-place rent by plan</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="inlineStr">
-        <is>
-          <t>Trade-out</t>
-        </is>
-      </c>
-      <c r="B145" s="5" t="n"/>
-      <c r="C145" s="5" t="n"/>
-      <c r="D145" s="5" t="n"/>
-      <c r="E145" s="5" t="n"/>
-      <c r="F145" s="5" t="n"/>
-      <c r="G145" s="5" t="n"/>
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll — plan</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>plan_new_lease_rent</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>Average rent on the plan's new leases inside the lookback window. Renewals are excluded.</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t>New-lease rent evidence</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>Trade-out</t>
+          <t>Rent roll — plan</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>cohort</t>
+          <t>plan_new_lease_count</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>New, Renewal, or First generation.</t>
+          <t>How many new leases the average rests on. A thin count is visible rather than implied.</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t>Lease trade-out report</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>New-vs-renewal growth evidence</t>
+          <t>Sample size</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>Trade-out</t>
+          <t>Rent roll — plan</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>cohort_leases</t>
+          <t>plan_market_rent_for_model</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>Leases in the cohort.</t>
+          <t>The plan's rent to underwrite: new-lease average where one exists, otherwise in-place. This is the column a financial model consumes.</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>Lease trade-out report</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>Sample size</t>
+          <t>Unit-mix market rent</t>
         </is>
       </c>
       <c r="G147" s="7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>Trade-out</t>
+          <t>Rent roll — plan</t>
         </is>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>cohort_prior_rent</t>
+          <t>plan_market_rent_basis</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>Average rent before the trade.</t>
+          <t>Which of the two fired, stated per plan.</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>Lease trade-out report</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
-          <t>Prior rent</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
-          <t>$1,706</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="6" t="inlineStr">
-        <is>
-          <t>Trade-out</t>
-        </is>
-      </c>
-      <c r="B149" s="6" t="inlineStr">
-        <is>
-          <t>cohort_new_rent_gross</t>
-        </is>
-      </c>
-      <c r="C149" s="6" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D149" s="7" t="inlineStr">
-        <is>
-          <t>Average new rent before concessions.</t>
-        </is>
-      </c>
-      <c r="E149" s="6" t="inlineStr">
-        <is>
-          <t>Lease trade-out report</t>
-        </is>
-      </c>
-      <c r="F149" s="7" t="inlineStr">
-        <is>
-          <t>Gross trade-out</t>
-        </is>
-      </c>
-      <c r="G149" s="7" t="inlineStr">
-        <is>
-          <t>$1,812</t>
-        </is>
-      </c>
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>Rent roll — totals</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="n"/>
+      <c r="C149" s="5" t="n"/>
+      <c r="D149" s="5" t="n"/>
+      <c r="E149" s="5" t="n"/>
+      <c r="F149" s="5" t="n"/>
+      <c r="G149" s="5" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>Trade-out</t>
+          <t>Rent roll — totals</t>
         </is>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>cohort_new_rent_effective</t>
+          <t>total_units</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D150" s="7" t="inlineStr">
         <is>
-          <t>Average new rent after concessions. Quoted separately from gross, because quoting one as the other is how a trade-out number becomes wrong.</t>
+          <t>Units on the roll.</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>Lease trade-out report</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>Effective trade-out</t>
+          <t>Unit count cross-check</t>
         </is>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
-          <t>$1,774</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>Trade-out</t>
+          <t>Rent roll — totals</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>cohort_gross_change_pct</t>
+          <t>occupied_units</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>Gross change over prior rent.</t>
+          <t>Occupied units.</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>Rent growth evidence</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="G151" s="7" t="inlineStr">
@@ -5475,22 +5475,22 @@
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>Trade-out</t>
+          <t>Rent roll — totals</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>cohort_effective_change_pct</t>
+          <t>vacant_units</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>Effective change over prior rent.</t>
+          <t>Vacant units.</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>Rent growth evidence</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr">
@@ -5512,22 +5512,22 @@
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>Trade-out</t>
+          <t>Rent roll — totals</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>absent_reason</t>
+          <t>occupancy</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>Why the block is empty, when no trade-out report exists. An empty block that says why is a deliverable; a block of plausible numbers is not.</t>
+          <t>Occupied over total.</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="F153" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Vacancy assumption</t>
         </is>
       </c>
       <c r="G153" s="7" t="inlineStr">
@@ -5547,74 +5547,98 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="5" t="inlineStr">
-        <is>
-          <t>Comps</t>
-        </is>
-      </c>
-      <c r="B154" s="5" t="n"/>
-      <c r="C154" s="5" t="n"/>
-      <c r="D154" s="5" t="n"/>
-      <c r="E154" s="5" t="n"/>
-      <c r="F154" s="5" t="n"/>
-      <c r="G154" s="5" t="n"/>
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll — totals</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>vacancy</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D154" s="7" t="inlineStr">
+        <is>
+          <t>One less occupancy. The physical-vacancy input.</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F154" s="7" t="inlineStr">
+        <is>
+          <t>Vacancy assumption</t>
+        </is>
+      </c>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>Comps</t>
+          <t>Rent roll — totals</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>comp_community</t>
+          <t>wavg_in_place_rent</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>Comparable community name.</t>
+          <t>Unit-weighted in-place rent across the property.</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F155" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>In-place rent</t>
         </is>
       </c>
       <c r="G155" s="7" t="inlineStr">
         <is>
-          <t>Alderwood Crossing</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>Comps</t>
+          <t>Rent roll — totals</t>
         </is>
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>comp_distance_mi</t>
+          <t>wavg_market_rent_for_model</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>Straight-line distance from the subject.</t>
+          <t>Unit-weighted market rent for model across the property.</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
@@ -5624,283 +5648,259 @@
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Market rent</t>
         </is>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>Comps</t>
+          <t>Rent roll — totals</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>comp_floor_plan</t>
+          <t>annualized_turnover</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>Comp floor plan the row describes. Comps are stated per plan, not as one blended community number.</t>
+          <t>Move-ins inside the lookback window, annualized against unit count.</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Turnover assumption</t>
         </is>
       </c>
       <c r="G157" s="7" t="inlineStr">
         <is>
-          <t>1BR-A</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>Comps</t>
+          <t>Rent roll — totals</t>
         </is>
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>comp_beds</t>
+          <t>lookback_months</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>Bedrooms in the comp plan.</t>
+          <t>Length of the new-lease window, measured back from the roll's as-of date.</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Supplied by the operator</t>
         </is>
       </c>
       <c r="F158" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>Comps</t>
+          <t>Rent roll — totals</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>comp_baths</t>
+          <t>new_tenant_tolerance_days</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>Bathrooms in the comp plan.</t>
+          <t>How far lease start may sit from move-in before a lease stops counting as a new tenant. A knob on the output, not a constant buried in code.</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Supplied by the operator</t>
         </is>
       </c>
       <c r="F159" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G159" s="7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>Comps</t>
+          <t>Rent roll — totals</t>
         </is>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>comp_sqft</t>
+          <t>roll_as_of</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>Square footage of the comp plan.</t>
+          <t>As-of date of the roll. Every window is measured from here.</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Rent roll export</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Analysis date</t>
         </is>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="6" t="inlineStr">
-        <is>
-          <t>Comps</t>
-        </is>
-      </c>
-      <c r="B161" s="6" t="inlineStr">
-        <is>
-          <t>comp_asking_rent</t>
-        </is>
-      </c>
-      <c r="C161" s="6" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D161" s="7" t="inlineStr">
-        <is>
-          <t>Advertised asking rent.</t>
-        </is>
-      </c>
-      <c r="E161" s="6" t="inlineStr">
-        <is>
-          <t>Operator's own weekly rent scrape</t>
-        </is>
-      </c>
-      <c r="F161" s="7" t="inlineStr">
-        <is>
-          <t>Market rent evidence</t>
-        </is>
-      </c>
-      <c r="G161" s="7" t="inlineStr">
-        <is>
-          <t>$1,495</t>
-        </is>
-      </c>
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>Trade-out</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="n"/>
+      <c r="C161" s="5" t="n"/>
+      <c r="D161" s="5" t="n"/>
+      <c r="E161" s="5" t="n"/>
+      <c r="F161" s="5" t="n"/>
+      <c r="G161" s="5" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>Comps</t>
+          <t>Trade-out</t>
         </is>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>comp_concession</t>
+          <t>cohort</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>Monthly value of the advertised concession.</t>
+          <t>New, Renewal, or First generation.</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Lease trade-out report</t>
         </is>
       </c>
       <c r="F162" s="7" t="inlineStr">
         <is>
-          <t>Concession assumption</t>
+          <t>New-vs-renewal growth evidence</t>
         </is>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
-          <t>$45</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>Comps</t>
+          <t>Trade-out</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>comp_net_effective_rent</t>
+          <t>cohort_leases</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>Asking rent less the amortized concession. Stated on every row — a concession-blind comp set is the most common way a rent assumption goes wrong.</t>
+          <t>Leases in the cohort.</t>
         </is>
       </c>
       <c r="E163" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Lease trade-out report</t>
         </is>
       </c>
       <c r="F163" s="7" t="inlineStr">
         <is>
-          <t>Market rent evidence</t>
+          <t>Sample size</t>
         </is>
       </c>
       <c r="G163" s="7" t="inlineStr">
         <is>
-          <t>$1,450</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>Comps</t>
+          <t>Trade-out</t>
         </is>
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>comp_asking_psf</t>
+          <t>cohort_prior_rent</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
@@ -5910,155 +5910,155 @@
       </c>
       <c r="D164" s="7" t="inlineStr">
         <is>
-          <t>Asking rent per square foot.</t>
+          <t>Average rent before the trade.</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Lease trade-out report</t>
         </is>
       </c>
       <c r="F164" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Prior rent</t>
         </is>
       </c>
       <c r="G164" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$1,706</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>Comps</t>
+          <t>Trade-out</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>comp_occupancy</t>
+          <t>cohort_new_rent_gross</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>Occupancy where the source published it.</t>
+          <t>Average new rent before concessions.</t>
         </is>
       </c>
       <c r="E165" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Lease trade-out report</t>
         </is>
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
-          <t>Market context</t>
+          <t>Gross trade-out</t>
         </is>
       </c>
       <c r="G165" s="7" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>$1,812</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>Comps</t>
+          <t>Trade-out</t>
         </is>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>comp_as_of</t>
+          <t>cohort_new_rent_effective</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D166" s="7" t="inlineStr">
         <is>
-          <t>When the row was scraped.</t>
+          <t>Average new rent after concessions. Quoted separately from gross, because quoting one as the other is how a trade-out number becomes wrong.</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Lease trade-out report</t>
         </is>
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Effective trade-out</t>
         </is>
       </c>
       <c r="G166" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>$1,774</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>Comps</t>
+          <t>Trade-out</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>comp_source</t>
+          <t>cohort_gross_change_pct</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>Always the operator's own weekly scrape. Licensed comp feeds are excluded by design and cannot be represented in this schema.</t>
+          <t>Gross change over prior rent.</t>
         </is>
       </c>
       <c r="E167" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F167" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Rent growth evidence</t>
         </is>
       </c>
       <c r="G167" s="7" t="inlineStr">
         <is>
-          <t>own weekly scrape</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>Comps</t>
+          <t>Trade-out</t>
         </is>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>compset_avg_asking</t>
+          <t>cohort_effective_change_pct</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D168" s="7" t="inlineStr">
         <is>
-          <t>Average asking rent across the comp set.</t>
+          <t>Effective change over prior rent.</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="F168" s="7" t="inlineStr">
         <is>
-          <t>Market rent benchmark</t>
+          <t>Rent growth evidence</t>
         </is>
       </c>
       <c r="G168" s="7" t="inlineStr">
@@ -6080,109 +6080,109 @@
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
         <is>
+          <t>Trade-out</t>
+        </is>
+      </c>
+      <c r="B169" s="6" t="inlineStr">
+        <is>
+          <t>absent_reason</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D169" s="7" t="inlineStr">
+        <is>
+          <t>Why the block is empty, when no trade-out report exists. An empty block that says why is a deliverable; a block of plausible numbers is not.</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="inlineStr">
+        <is>
           <t>Comps</t>
         </is>
       </c>
-      <c r="B169" s="6" t="inlineStr">
-        <is>
-          <t>compset_avg_net_effective</t>
-        </is>
-      </c>
-      <c r="C169" s="6" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D169" s="7" t="inlineStr">
-        <is>
-          <t>Average net effective rent across the comp set.</t>
-        </is>
-      </c>
-      <c r="E169" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F169" s="7" t="inlineStr">
-        <is>
-          <t>Market rent benchmark</t>
-        </is>
-      </c>
-      <c r="G169" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="6" t="inlineStr">
+      <c r="B170" s="5" t="n"/>
+      <c r="C170" s="5" t="n"/>
+      <c r="D170" s="5" t="n"/>
+      <c r="E170" s="5" t="n"/>
+      <c r="F170" s="5" t="n"/>
+      <c r="G170" s="5" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="6" t="inlineStr">
         <is>
           <t>Comps</t>
         </is>
       </c>
-      <c r="B170" s="6" t="inlineStr">
-        <is>
-          <t>subject_vs_compset_spread</t>
-        </is>
-      </c>
-      <c r="C170" s="6" t="inlineStr">
-        <is>
-          <t>percent</t>
-        </is>
-      </c>
-      <c r="D170" s="7" t="inlineStr">
-        <is>
-          <t>Subject market rent over comp-set net effective, less one.</t>
-        </is>
-      </c>
-      <c r="E170" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F170" s="7" t="inlineStr">
-        <is>
-          <t>Rent positioning</t>
-        </is>
-      </c>
-      <c r="G170" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="5" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="B171" s="5" t="n"/>
-      <c r="C171" s="5" t="n"/>
-      <c r="D171" s="5" t="n"/>
-      <c r="E171" s="5" t="n"/>
-      <c r="F171" s="5" t="n"/>
-      <c r="G171" s="5" t="n"/>
+      <c r="B171" s="6" t="inlineStr">
+        <is>
+          <t>comp_community</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>Comparable community name.</t>
+        </is>
+      </c>
+      <c r="E171" s="6" t="inlineStr">
+        <is>
+          <t>Operator's own weekly rent scrape</t>
+        </is>
+      </c>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>Comp set</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="inlineStr">
+        <is>
+          <t>Alderwood Crossing</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="6" t="inlineStr">
         <is>
-          <t>Demand</t>
+          <t>Comps</t>
         </is>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>demand_ring</t>
+          <t>comp_distance_mi</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D172" s="7" t="inlineStr">
         <is>
-          <t>Drive-ring the row describes: 1, 3, 5, or 10 miles, or the MSA.</t>
+          <t>Straight-line distance from the subject.</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
@@ -6192,269 +6192,293 @@
       </c>
       <c r="F172" s="7" t="inlineStr">
         <is>
-          <t>Market summary</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G172" s="7" t="inlineStr">
         <is>
-          <t>1 mi</t>
+          <t>0.7</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
         <is>
-          <t>Demand</t>
+          <t>Comps</t>
         </is>
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>demand_population</t>
+          <t>comp_floor_plan</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>Population in the ring.</t>
+          <t>Comp floor plan the row describes. Comps are stated per plan, not as one blended community number.</t>
         </is>
       </c>
       <c r="E173" s="6" t="inlineStr">
         <is>
-          <t>Public demographic data</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F173" s="7" t="inlineStr">
         <is>
-          <t>Market summary</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G173" s="7" t="inlineStr">
         <is>
-          <t>9,840</t>
+          <t>1BR-A</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="6" t="inlineStr">
         <is>
-          <t>Demand</t>
+          <t>Comps</t>
         </is>
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>demand_households</t>
+          <t>comp_beds</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D174" s="7" t="inlineStr">
         <is>
-          <t>Households in the ring.</t>
+          <t>Bedrooms in the comp plan.</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>Public demographic data</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F174" s="7" t="inlineStr">
         <is>
-          <t>Market summary</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G174" s="7" t="inlineStr">
         <is>
-          <t>4,020</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
         <is>
-          <t>Demand</t>
+          <t>Comps</t>
         </is>
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>demand_median_income</t>
+          <t>comp_baths</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>Median household income in the ring.</t>
+          <t>Bathrooms in the comp plan.</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t>Public demographic data</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F175" s="7" t="inlineStr">
         <is>
-          <t>Affordability check</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G175" s="7" t="inlineStr">
         <is>
-          <t>$78,400</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>Demand</t>
+          <t>Comps</t>
         </is>
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>demand_jobs</t>
+          <t>comp_sqft</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D176" s="7" t="inlineStr">
         <is>
-          <t>Jobs located in the ring.</t>
+          <t>Square footage of the comp plan.</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>Public demographic data</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F176" s="7" t="inlineStr">
         <is>
-          <t>Market summary</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G176" s="7" t="inlineStr">
         <is>
-          <t>3,150</t>
+          <t>735</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>Demand</t>
+          <t>Comps</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>demand_pop_growth_5yr</t>
+          <t>comp_asking_rent</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>Five-year population growth in the ring.</t>
+          <t>Advertised asking rent.</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
         <is>
-          <t>Public demographic data</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>Growth assumption evidence</t>
+          <t>Market rent evidence</t>
         </is>
       </c>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>$1,495</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="6" t="inlineStr">
         <is>
-          <t>Demand</t>
+          <t>Comps</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>demand_renter_share</t>
+          <t>comp_concession</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D178" s="7" t="inlineStr">
         <is>
-          <t>Share of ring households that rent.</t>
+          <t>Monthly value of the advertised concession.</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>Public demographic data</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F178" s="7" t="inlineStr">
         <is>
-          <t>Demand context</t>
+          <t>Concession assumption</t>
         </is>
       </c>
       <c r="G178" s="7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>$45</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="5" t="inlineStr">
-        <is>
-          <t>Supply</t>
-        </is>
-      </c>
-      <c r="B179" s="5" t="n"/>
-      <c r="C179" s="5" t="n"/>
-      <c r="D179" s="5" t="n"/>
-      <c r="E179" s="5" t="n"/>
-      <c r="F179" s="5" t="n"/>
-      <c r="G179" s="5" t="n"/>
+      <c r="A179" s="6" t="inlineStr">
+        <is>
+          <t>Comps</t>
+        </is>
+      </c>
+      <c r="B179" s="6" t="inlineStr">
+        <is>
+          <t>comp_net_effective_rent</t>
+        </is>
+      </c>
+      <c r="C179" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D179" s="7" t="inlineStr">
+        <is>
+          <t>Asking rent less the amortized concession. Stated on every row — a concession-blind comp set is the most common way a rent assumption goes wrong.</t>
+        </is>
+      </c>
+      <c r="E179" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>Market rent evidence</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="inlineStr">
+        <is>
+          <t>$1,450</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="6" t="inlineStr">
         <is>
-          <t>Supply</t>
+          <t>Comps</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>supply_ring</t>
+          <t>comp_asking_psf</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D180" s="7" t="inlineStr">
         <is>
-          <t>Ring the supply row describes.</t>
+          <t>Asking rent per square foot.</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -6464,145 +6488,145 @@
       </c>
       <c r="F180" s="7" t="inlineStr">
         <is>
-          <t>Competing supply</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G180" s="7" t="inlineStr">
         <is>
-          <t>1 mi</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>Supply</t>
+          <t>Comps</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>supply_stage</t>
+          <t>comp_occupancy</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>Entitlement, permitted, under construction, or delivered in the last 24 months. Stage is stated because entitled units and delivered units are not the same risk.</t>
+          <t>Occupancy where the source published it.</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
         <is>
-          <t>Public permit / entitlement records</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F181" s="7" t="inlineStr">
         <is>
-          <t>Competing supply</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G181" s="7" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>94.0%</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="6" t="inlineStr">
         <is>
-          <t>Supply</t>
+          <t>Comps</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>supply_projects</t>
+          <t>comp_as_of</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D182" s="7" t="inlineStr">
         <is>
-          <t>Projects at that ring and stage.</t>
+          <t>When the row was scraped.</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>Public permit / entitlement records</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F182" s="7" t="inlineStr">
         <is>
-          <t>Competing supply</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G182" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>Supply</t>
+          <t>Comps</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>supply_units</t>
+          <t>comp_source</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>Units at that ring and stage.</t>
+          <t>Always the operator's own weekly scrape. Licensed comp feeds are excluded by design and cannot be represented in this schema.</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>Public permit / entitlement records</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F183" s="7" t="inlineStr">
         <is>
-          <t>Competing supply / absorption</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G183" s="7" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>own weekly scrape</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="6" t="inlineStr">
         <is>
-          <t>Supply</t>
+          <t>Comps</t>
         </is>
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>supply_ring_total_units</t>
+          <t>compset_avg_asking</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D184" s="7" t="inlineStr">
         <is>
-          <t>All pipeline units in the ring across stages.</t>
+          <t>Average asking rent across the comp set.</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -6612,7 +6636,7 @@
       </c>
       <c r="F184" s="7" t="inlineStr">
         <is>
-          <t>Competing supply</t>
+          <t>Market rent benchmark</t>
         </is>
       </c>
       <c r="G184" s="7" t="inlineStr">
@@ -6624,35 +6648,579 @@
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
         <is>
+          <t>Comps</t>
+        </is>
+      </c>
+      <c r="B185" s="6" t="inlineStr">
+        <is>
+          <t>compset_avg_net_effective</t>
+        </is>
+      </c>
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D185" s="7" t="inlineStr">
+        <is>
+          <t>Average net effective rent across the comp set.</t>
+        </is>
+      </c>
+      <c r="E185" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F185" s="7" t="inlineStr">
+        <is>
+          <t>Market rent benchmark</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>Comps</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
+        <is>
+          <t>subject_vs_compset_spread</t>
+        </is>
+      </c>
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D186" s="7" t="inlineStr">
+        <is>
+          <t>Subject market rent over comp-set net effective, less one.</t>
+        </is>
+      </c>
+      <c r="E186" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F186" s="7" t="inlineStr">
+        <is>
+          <t>Rent positioning</t>
+        </is>
+      </c>
+      <c r="G186" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="n"/>
+      <c r="C187" s="5" t="n"/>
+      <c r="D187" s="5" t="n"/>
+      <c r="E187" s="5" t="n"/>
+      <c r="F187" s="5" t="n"/>
+      <c r="G187" s="5" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
+        <is>
+          <t>demand_ring</t>
+        </is>
+      </c>
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D188" s="7" t="inlineStr">
+        <is>
+          <t>Drive-ring the row describes: 1, 3, 5, or 10 miles, or the MSA.</t>
+        </is>
+      </c>
+      <c r="E188" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F188" s="7" t="inlineStr">
+        <is>
+          <t>Market summary</t>
+        </is>
+      </c>
+      <c r="G188" s="7" t="inlineStr">
+        <is>
+          <t>1 mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B189" s="6" t="inlineStr">
+        <is>
+          <t>demand_population</t>
+        </is>
+      </c>
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D189" s="7" t="inlineStr">
+        <is>
+          <t>Population in the ring.</t>
+        </is>
+      </c>
+      <c r="E189" s="6" t="inlineStr">
+        <is>
+          <t>Public demographic data</t>
+        </is>
+      </c>
+      <c r="F189" s="7" t="inlineStr">
+        <is>
+          <t>Market summary</t>
+        </is>
+      </c>
+      <c r="G189" s="7" t="inlineStr">
+        <is>
+          <t>9,840</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
+        <is>
+          <t>demand_households</t>
+        </is>
+      </c>
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D190" s="7" t="inlineStr">
+        <is>
+          <t>Households in the ring.</t>
+        </is>
+      </c>
+      <c r="E190" s="6" t="inlineStr">
+        <is>
+          <t>Public demographic data</t>
+        </is>
+      </c>
+      <c r="F190" s="7" t="inlineStr">
+        <is>
+          <t>Market summary</t>
+        </is>
+      </c>
+      <c r="G190" s="7" t="inlineStr">
+        <is>
+          <t>4,020</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="6" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B191" s="6" t="inlineStr">
+        <is>
+          <t>demand_median_income</t>
+        </is>
+      </c>
+      <c r="C191" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D191" s="7" t="inlineStr">
+        <is>
+          <t>Median household income in the ring.</t>
+        </is>
+      </c>
+      <c r="E191" s="6" t="inlineStr">
+        <is>
+          <t>Public demographic data</t>
+        </is>
+      </c>
+      <c r="F191" s="7" t="inlineStr">
+        <is>
+          <t>Affordability check</t>
+        </is>
+      </c>
+      <c r="G191" s="7" t="inlineStr">
+        <is>
+          <t>$78,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="6" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B192" s="6" t="inlineStr">
+        <is>
+          <t>demand_jobs</t>
+        </is>
+      </c>
+      <c r="C192" s="6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D192" s="7" t="inlineStr">
+        <is>
+          <t>Jobs located in the ring.</t>
+        </is>
+      </c>
+      <c r="E192" s="6" t="inlineStr">
+        <is>
+          <t>Public demographic data</t>
+        </is>
+      </c>
+      <c r="F192" s="7" t="inlineStr">
+        <is>
+          <t>Market summary</t>
+        </is>
+      </c>
+      <c r="G192" s="7" t="inlineStr">
+        <is>
+          <t>3,150</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="6" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B193" s="6" t="inlineStr">
+        <is>
+          <t>demand_pop_growth_5yr</t>
+        </is>
+      </c>
+      <c r="C193" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D193" s="7" t="inlineStr">
+        <is>
+          <t>Five-year population growth in the ring.</t>
+        </is>
+      </c>
+      <c r="E193" s="6" t="inlineStr">
+        <is>
+          <t>Public demographic data</t>
+        </is>
+      </c>
+      <c r="F193" s="7" t="inlineStr">
+        <is>
+          <t>Growth assumption evidence</t>
+        </is>
+      </c>
+      <c r="G193" s="7" t="inlineStr">
+        <is>
+          <t>6.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="6" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B194" s="6" t="inlineStr">
+        <is>
+          <t>demand_renter_share</t>
+        </is>
+      </c>
+      <c r="C194" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D194" s="7" t="inlineStr">
+        <is>
+          <t>Share of ring households that rent.</t>
+        </is>
+      </c>
+      <c r="E194" s="6" t="inlineStr">
+        <is>
+          <t>Public demographic data</t>
+        </is>
+      </c>
+      <c r="F194" s="7" t="inlineStr">
+        <is>
+          <t>Demand context</t>
+        </is>
+      </c>
+      <c r="G194" s="7" t="inlineStr">
+        <is>
+          <t>44.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="inlineStr">
+        <is>
           <t>Supply</t>
         </is>
       </c>
-      <c r="B185" s="6" t="inlineStr">
+      <c r="B195" s="5" t="n"/>
+      <c r="C195" s="5" t="n"/>
+      <c r="D195" s="5" t="n"/>
+      <c r="E195" s="5" t="n"/>
+      <c r="F195" s="5" t="n"/>
+      <c r="G195" s="5" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="6" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B196" s="6" t="inlineStr">
+        <is>
+          <t>supply_ring</t>
+        </is>
+      </c>
+      <c r="C196" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D196" s="7" t="inlineStr">
+        <is>
+          <t>Ring the supply row describes.</t>
+        </is>
+      </c>
+      <c r="E196" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F196" s="7" t="inlineStr">
+        <is>
+          <t>Competing supply</t>
+        </is>
+      </c>
+      <c r="G196" s="7" t="inlineStr">
+        <is>
+          <t>1 mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="6" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B197" s="6" t="inlineStr">
+        <is>
+          <t>supply_stage</t>
+        </is>
+      </c>
+      <c r="C197" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D197" s="7" t="inlineStr">
+        <is>
+          <t>Entitlement, permitted, under construction, or delivered in the last 24 months. Stage is stated because entitled units and delivered units are not the same risk.</t>
+        </is>
+      </c>
+      <c r="E197" s="6" t="inlineStr">
+        <is>
+          <t>Public permit / entitlement records</t>
+        </is>
+      </c>
+      <c r="F197" s="7" t="inlineStr">
+        <is>
+          <t>Competing supply</t>
+        </is>
+      </c>
+      <c r="G197" s="7" t="inlineStr">
+        <is>
+          <t>Entitlement</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B198" s="6" t="inlineStr">
+        <is>
+          <t>supply_projects</t>
+        </is>
+      </c>
+      <c r="C198" s="6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D198" s="7" t="inlineStr">
+        <is>
+          <t>Projects at that ring and stage.</t>
+        </is>
+      </c>
+      <c r="E198" s="6" t="inlineStr">
+        <is>
+          <t>Public permit / entitlement records</t>
+        </is>
+      </c>
+      <c r="F198" s="7" t="inlineStr">
+        <is>
+          <t>Competing supply</t>
+        </is>
+      </c>
+      <c r="G198" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B199" s="6" t="inlineStr">
+        <is>
+          <t>supply_units</t>
+        </is>
+      </c>
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D199" s="7" t="inlineStr">
+        <is>
+          <t>Units at that ring and stage.</t>
+        </is>
+      </c>
+      <c r="E199" s="6" t="inlineStr">
+        <is>
+          <t>Public permit / entitlement records</t>
+        </is>
+      </c>
+      <c r="F199" s="7" t="inlineStr">
+        <is>
+          <t>Competing supply / absorption</t>
+        </is>
+      </c>
+      <c r="G199" s="7" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="6" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B200" s="6" t="inlineStr">
+        <is>
+          <t>supply_ring_total_units</t>
+        </is>
+      </c>
+      <c r="C200" s="6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D200" s="7" t="inlineStr">
+        <is>
+          <t>All pipeline units in the ring across stages.</t>
+        </is>
+      </c>
+      <c r="E200" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F200" s="7" t="inlineStr">
+        <is>
+          <t>Competing supply</t>
+        </is>
+      </c>
+      <c r="G200" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="6" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B201" s="6" t="inlineStr">
         <is>
           <t>supply_pct_of_ring_stock</t>
         </is>
       </c>
-      <c r="C185" s="6" t="inlineStr">
+      <c r="C201" s="6" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="D185" s="7" t="inlineStr">
+      <c r="D201" s="7" t="inlineStr">
         <is>
           <t>Pipeline units as a share of the ring's existing stock, where stock is known.</t>
         </is>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="E201" s="6" t="inlineStr">
         <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="F185" s="7" t="inlineStr">
+      <c r="F201" s="7" t="inlineStr">
         <is>
           <t>Supply pressure</t>
         </is>
       </c>
-      <c r="G185" s="7" t="inlineStr">
+      <c r="G201" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6673,11 +7241,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6729,7 +7298,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>42/42 (100%)</t>
+          <t>50/50 (100%)</t>
         </is>
       </c>
     </row>
@@ -6741,25 +7310,30 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
+          <t>Value as published</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
           <t>Source document</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Where in it</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>How</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Built from</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Supporting quote / note</t>
         </is>
@@ -6773,25 +7347,34 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
           <t>Vendored state rate table</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>closing_costs.py</t>
-        </is>
-      </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
+          <t>closing_costs.MORTGAGE_TAX</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
           <t>computed</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>pricing.price_per_unit, summary.state</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="n"/>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>closing_costs.loan_amount, summary.state</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Computed on the LOAN, never on the price. With no loan amount the line is reported as not asserted rather than inferred at 100% leverage.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -6801,25 +7384,34 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
           <t>Vendored state rate table</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>closing_costs.py</t>
-        </is>
-      </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
+          <t>closing_costs.TRANSFER_TAX</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
           <t>computed</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>pricing.price_per_unit, summary.state</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="n"/>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>pricing.price_per_unit, pricing.unit_count, summary.state, closing_costs.price</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Rate applied to price_per_unit x unit_count. Per-unit statutes round the consideration up.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -6829,21 +7421,26 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
+          <t>10 entries</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
           <t>Synthetic weekly rent scrape</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>Own weekly scrape; asking and net effective stated separately.</t>
         </is>
@@ -6857,21 +7454,26 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
+          <t>5 entries</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
           <t>Synthetic public data extract</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>Ring demographics.</t>
         </is>
@@ -6885,21 +7487,26 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
+          <t>215,000</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
           <t>Supplied by the operator</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>Illustrative. Inside the band a per-unit sale price occupies.</t>
         </is>
@@ -6913,25 +7520,30 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
           <t>Synthetic rent roll export</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Rent Roll!A:A</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>derived</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>summary.unit_count</t>
         </is>
       </c>
-      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="13" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -6941,21 +7553,26 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
           <t>Synthetic rent roll export</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>Rent Roll!A2</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E15" s="13" t="n"/>
       <c r="F15" s="12" t="n"/>
+      <c r="G15" s="13" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -6965,21 +7582,26 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
           <t>Supplied by the operator</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>Analysis knob.</t>
         </is>
@@ -6993,21 +7615,26 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
           <t>Supplied by the operator</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>Analysis knob.</t>
         </is>
@@ -7021,21 +7648,26 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
+          <t>180 entries</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
           <t>Synthetic rent roll export</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>Rent Roll!A4:K183</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>Unit identifiers only; the source's resident-name column is never read.</t>
         </is>
@@ -7049,21 +7681,26 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
+          <t>23,000,000</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
           <t>Synthetic county tax record</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Valuation notice</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E19" s="13" t="n"/>
       <c r="F19" s="12" t="n"/>
+      <c r="G19" s="13" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
@@ -7073,21 +7710,26 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
           <t>Synthetic county tax record</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>Rate table</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E20" s="13" t="n"/>
       <c r="F20" s="12" t="n"/>
+      <c r="G20" s="13" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -7097,21 +7739,26 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
+          <t>Sample City</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
           <t>Synthetic offering memorandum</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>p.4</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E21" s="13" t="n"/>
       <c r="F21" s="12" t="n"/>
+      <c r="G21" s="13" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
@@ -7121,21 +7768,26 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
+          <t>Stabilized</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
           <t>Synthetic offering memorandum</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>p.6</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E22" s="13" t="n"/>
       <c r="F22" s="12" t="n"/>
+      <c r="G22" s="13" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
@@ -7145,21 +7797,26 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
+          <t>Example County</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
           <t>Synthetic offering memorandum</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>p.4</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E23" s="13" t="n"/>
       <c r="F23" s="12" t="n"/>
+      <c r="G23" s="13" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -7169,21 +7826,26 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
+          <t>Fixture Park</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
           <t>Synthetic offering memorandum</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>p.1</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>Fixture Park</t>
         </is>
@@ -7197,21 +7859,26 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
+          <t>On the market</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
           <t>Synthetic offering memorandum</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>p.2</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E25" s="13" t="n"/>
       <c r="F25" s="12" t="n"/>
+      <c r="G25" s="13" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -7221,21 +7888,26 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
+          <t>Delivered 2019; fully stabilized since 2021</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
           <t>Synthetic offering memorandum</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>p.6</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E26" s="13" t="n"/>
       <c r="F26" s="12" t="n"/>
+      <c r="G26" s="13" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
@@ -7245,21 +7917,26 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
+          <t>39,600,000</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
           <t>Supplied by the operator</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>Operator's own estimate.</t>
         </is>
@@ -7273,27 +7950,32 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
+          <t>1,795.36</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Unit Mix Summary!H</t>
-        </is>
-      </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
+          <t>Unit Mix Summary!E</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
           <t>computed</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>rent_roll.units</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>Occupied units, weighted.</t>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Occupied units, straight off the roll.</t>
         </is>
       </c>
     </row>
@@ -7305,25 +7987,30 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
+          <t>Listing brokerage</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>derived</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>summary.seller_entity</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>Generic label; no firm or individual is named in a published file.</t>
         </is>
@@ -7337,25 +8024,30 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
+          <t>1,834.78</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>Unit Mix Summary!K</t>
-        </is>
-      </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
+          <t>Unit Mix Summary!H</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
           <t>computed</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>rent_roll.units</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>New-lease average where a plan has new leases in the window, else in-place. Never a blend.</t>
         </is>
@@ -7369,25 +8061,30 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
+          <t>Sample City MSA</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>derived</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>summary.city, summary.state</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>Metro assigned from the city/state pair.</t>
         </is>
@@ -7401,21 +8098,26 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
+          <t>$215,000 per unit (illustrative)</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
           <t>Supplied by the operator</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>Illustrative figure supplied directly; not a quote or an offer.</t>
         </is>
@@ -7429,21 +8131,26 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
+          <t>180 units across six plans: 62 one-bedroom (720–795 SF), 78 two-bedroom (1,050–1,140 SF…</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
           <t>Synthetic offering memorandum</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>p.7</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E33" s="13" t="n"/>
       <c r="F33" s="12" t="n"/>
+      <c r="G33" s="13" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -7453,21 +8160,26 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
+          <t>MF</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
           <t>Synthetic offering memorandum</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>p.6</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E34" s="13" t="n"/>
       <c r="F34" s="12" t="n"/>
+      <c r="G34" s="13" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
@@ -7477,21 +8189,26 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
+          <t>Example Creek Elementary</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
           <t>Synthetic public data extract</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>School attendance lookup</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E35" s="13" t="n"/>
       <c r="F35" s="12" t="n"/>
+      <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
@@ -7501,21 +8218,26 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
+          <t>Sample City High</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
           <t>Synthetic public data extract</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>School attendance lookup</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E36" s="13" t="n"/>
       <c r="F36" s="12" t="n"/>
+      <c r="G36" s="13" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -7525,21 +8247,26 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
+          <t>Example Ridge Middle</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
           <t>Synthetic public data extract</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>School attendance lookup</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E37" s="13" t="n"/>
       <c r="F37" s="12" t="n"/>
+      <c r="G37" s="13" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -7549,21 +8276,26 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
+          <t>Sample City Residential Holdings LLC</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
           <t>Synthetic offering memorandum</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>p.2</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E38" s="13" t="n"/>
       <c r="F38" s="12" t="n"/>
+      <c r="G38" s="13" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -7573,21 +8305,26 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
           <t>Synthetic offering memorandum</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>p.4</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E39" s="13" t="n"/>
       <c r="F39" s="12" t="n"/>
+      <c r="G39" s="13" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
@@ -7597,21 +8334,26 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
+          <t>1400 Example Parkway</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
           <t>Synthetic offering memorandum</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>p.4</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E40" s="13" t="n"/>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F40" s="12" t="n"/>
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>1400 Example Parkway</t>
         </is>
@@ -7625,21 +8367,26 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
+          <t>Three-story garden, surface parked</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
           <t>Synthetic offering memorandum</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>p.6</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F41" s="12" t="n"/>
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>Three-story garden, surface parked</t>
         </is>
@@ -7653,21 +8400,26 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
+          <t>SYN-0000</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
           <t>Synthetic county tax record</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>Rate table</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E42" s="13" t="n"/>
       <c r="F42" s="12" t="n"/>
+      <c r="G42" s="13" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -7677,21 +8429,26 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
+          <t>Assessed value (synthetic)</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
           <t>Synthetic county tax record</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>Valuation notice</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E43" s="13" t="n"/>
       <c r="F43" s="12" t="n"/>
+      <c r="G43" s="13" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -7701,21 +8458,26 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
+          <t>Synthetic basis. On a real deal this row states what the basis IS in that state and whe…</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
           <t>Synthetic county tax record</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>Valuation notice</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E44" s="13" t="n"/>
       <c r="F44" s="12" t="n"/>
+      <c r="G44" s="13" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -7725,21 +8487,26 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
+          <t>494,040</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
           <t>Synthetic county tax record</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>Tax bill</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E45" s="13" t="n"/>
       <c r="F45" s="12" t="n"/>
+      <c r="G45" s="13" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -7749,21 +8516,26 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
+          <t>2,025</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
           <t>Synthetic county tax record</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>Tax bill</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E46" s="13" t="n"/>
       <c r="F46" s="12" t="n"/>
+      <c r="G46" s="13" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -7773,21 +8545,26 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
           <t>Synthetic county tax record</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>Rate table</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E47" s="13" t="n"/>
       <c r="F47" s="12" t="n"/>
+      <c r="G47" s="13" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -7797,21 +8574,26 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
           <t>Synthetic county tax record</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>Valuation notice</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="E48" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E48" s="13" t="n"/>
       <c r="F48" s="12" t="n"/>
+      <c r="G48" s="13" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -7821,21 +8603,26 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
+          <t>SYN-000-00-000</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
           <t>Synthetic county tax record</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Parcel record</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E49" s="13" t="n"/>
       <c r="F49" s="12" t="n"/>
+      <c r="G49" s="13" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -7845,21 +8632,26 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
           <t>Synthetic county tax record</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>Rate table, synthetic district</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E50" s="13" t="n"/>
       <c r="F50" s="12" t="n"/>
+      <c r="G50" s="13" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -7869,25 +8661,30 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
           <t>Synthetic rent roll export</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>Rent Roll!A:A</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>derived</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <t>rent_roll.units</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>Distinct unit identifiers on the roll.</t>
         </is>
@@ -7901,21 +8698,26 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
+          <t>2,019</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
           <t>Synthetic offering memorandum</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>p.6</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E52" s="13" t="n"/>
       <c r="F52" s="12" t="n"/>
+      <c r="G52" s="13" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -7925,21 +8727,26 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
+          <t>75000</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
           <t>Synthetic offering memorandum</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>p.4</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E53" s="13" t="n"/>
       <c r="F53" s="12" t="n"/>
+      <c r="G53" s="13" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
@@ -7949,21 +8756,26 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
+          <t>12 entries</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
           <t>Synthetic public data extract</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E54" s="13" t="n"/>
-      <c r="F54" s="7" t="inlineStr">
+      <c r="F54" s="12" t="n"/>
+      <c r="G54" s="7" t="inlineStr">
         <is>
           <t>Permit and entitlement records.</t>
         </is>
@@ -7977,21 +8789,26 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
+          <t>12 entries</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
           <t>Synthetic trailing-twelve income statement</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>T-12!C8:N8</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E55" s="13" t="n"/>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="F55" s="12" t="n"/>
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>Twelve consecutive month-end columns; direction detected from the labels.</t>
         </is>
@@ -8005,21 +8822,26 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
+          <t>5 keys</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
           <t>Synthetic trailing-twelve income statement</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>T-12!O</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="E56" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E56" s="13" t="n"/>
-      <c r="F56" s="7" t="inlineStr">
+      <c r="F56" s="12" t="n"/>
+      <c r="G56" s="7" t="inlineStr">
         <is>
           <t>The statement's own printed subtotals, kept for the cross-tie.</t>
         </is>
@@ -8033,25 +8855,30 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
           <t>Synthetic rent roll export</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>derived</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t>summary.unit_count</t>
         </is>
       </c>
-      <c r="F57" s="12" t="n"/>
+      <c r="G57" s="13" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
@@ -8061,21 +8888,26 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
+          <t>3 entries</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
           <t>Synthetic lease trade-out report</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="E58" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E58" s="13" t="n"/>
-      <c r="F58" s="7" t="inlineStr">
+      <c r="F58" s="12" t="n"/>
+      <c r="G58" s="7" t="inlineStr">
         <is>
           <t>Cohort averages.</t>
         </is>

--- a/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
+++ b/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G201"/>
+  <dimension ref="A1:G210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="G172" s="7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
@@ -6246,22 +6246,22 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>comp_beds</t>
+          <t>comp_tier</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D174" s="7" t="inlineStr">
         <is>
-          <t>Bedrooms in the comp plan.</t>
+          <t>1 = top comps (the closest five matching the subject's product and vintage), 2 = additional comps (the next fifteen). Tier 3 is identity-only and carries no rent.</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F174" s="7" t="inlineStr">
@@ -6283,17 +6283,17 @@
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>comp_baths</t>
+          <t>comp_year_built</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>Bathrooms in the comp plan.</t>
+          <t>Comp vintage where one is published. Blank means nobody published one — the tracker has no year-built column — never that the community is new.</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="G175" s="7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2,021</t>
         </is>
       </c>
     </row>
@@ -6320,17 +6320,17 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>comp_sqft</t>
+          <t>comp_year_built_source</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D176" s="7" t="inlineStr">
         <is>
-          <t>Square footage of the comp plan.</t>
+          <t>Where that year came from. Blank alongside a blank year; a year with no source is rejected at validation.</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="F176" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G176" s="7" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>vendor note on the tracked community record</t>
         </is>
       </c>
     </row>
@@ -6357,17 +6357,17 @@
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>comp_asking_rent</t>
+          <t>nearby_community</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>Advertised asking rent.</t>
+          <t>A tracked community inside the radius that is NOT a comp.</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
@@ -6377,12 +6377,12 @@
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>Market rent evidence</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>$1,495</t>
+          <t>Rushmere Townhomes</t>
         </is>
       </c>
     </row>
@@ -6394,17 +6394,17 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>comp_concession</t>
+          <t>nearby_address</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D178" s="7" t="inlineStr">
         <is>
-          <t>Monthly value of the advertised concession.</t>
+          <t>Its address, so the reader can place it.</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="F178" s="7" t="inlineStr">
         <is>
-          <t>Concession assumption</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G178" s="7" t="inlineStr">
         <is>
-          <t>$45</t>
+          <t>375 Sample Street, Demo City</t>
         </is>
       </c>
     </row>
@@ -6431,17 +6431,17 @@
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>comp_net_effective_rent</t>
+          <t>nearby_distance_mi</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>Asking rent less the amortized concession. Stated on every row — a concession-blind comp set is the most common way a rent assumption goes wrong.</t>
+          <t>Distance from the subject.</t>
         </is>
       </c>
       <c r="E179" s="6" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
-          <t>Market rent evidence</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G179" s="7" t="inlineStr">
         <is>
-          <t>$1,450</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -6468,32 +6468,32 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>comp_asking_psf</t>
+          <t>nearby_units</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D180" s="7" t="inlineStr">
         <is>
-          <t>Asking rent per square foot.</t>
+          <t>Unit count where the registry has one.</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F180" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G180" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>96</t>
         </is>
       </c>
     </row>
@@ -6505,22 +6505,22 @@
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>comp_occupancy</t>
+          <t>nearby_reason</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>Occupancy where the source published it.</t>
+          <t>Why it is not a comp: wrong product, vintage outside the band, no quoted rent, excluded by the tracker, or simply beyond the closest twenty. The column that answers 'why isn't the property across the street in your comp set?'.</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F181" s="7" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="G181" s="7" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>different product: tracked as bfr, subject is MF</t>
         </is>
       </c>
     </row>
@@ -6542,22 +6542,22 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>comp_as_of</t>
+          <t>compset_vintage_footnote</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D182" s="7" t="inlineStr">
         <is>
-          <t>When the row was scraped.</t>
+          <t>The disclosure on the detailed tiers: the band applied, and whether some communities carried no year and so could not be tested.</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F182" s="7" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="G182" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>Vintage filter applied where year known: +/-10 years of the subject's year built. 1 of 11 communities shown carry no published year and were matched on distance and product only.</t>
         </is>
       </c>
     </row>
@@ -6579,17 +6579,17 @@
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>comp_source</t>
+          <t>comp_beds</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>Always the operator's own weekly scrape. Licensed comp feeds are excluded by design and cannot be represented in this schema.</t>
+          <t>Bedrooms in the comp plan.</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="F183" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G183" s="7" t="inlineStr">
         <is>
-          <t>own weekly scrape</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6616,32 +6616,32 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>compset_avg_asking</t>
+          <t>comp_baths</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D184" s="7" t="inlineStr">
         <is>
-          <t>Average asking rent across the comp set.</t>
+          <t>Bathrooms in the comp plan.</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F184" s="7" t="inlineStr">
         <is>
-          <t>Market rent benchmark</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G184" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -6653,32 +6653,32 @@
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>compset_avg_net_effective</t>
+          <t>comp_sqft</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D185" s="7" t="inlineStr">
         <is>
-          <t>Average net effective rent across the comp set.</t>
+          <t>Square footage of the comp plan.</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F185" s="7" t="inlineStr">
         <is>
-          <t>Market rent benchmark</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G185" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>735</t>
         </is>
       </c>
     </row>
@@ -6690,67 +6690,91 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>subject_vs_compset_spread</t>
+          <t>comp_asking_rent</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D186" s="7" t="inlineStr">
         <is>
-          <t>Subject market rent over comp-set net effective, less one.</t>
+          <t>Advertised asking rent.</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F186" s="7" t="inlineStr">
         <is>
-          <t>Rent positioning</t>
+          <t>Market rent evidence</t>
         </is>
       </c>
       <c r="G186" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$1,450</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="5" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="B187" s="5" t="n"/>
-      <c r="C187" s="5" t="n"/>
-      <c r="D187" s="5" t="n"/>
-      <c r="E187" s="5" t="n"/>
-      <c r="F187" s="5" t="n"/>
-      <c r="G187" s="5" t="n"/>
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>Comps</t>
+        </is>
+      </c>
+      <c r="B187" s="6" t="inlineStr">
+        <is>
+          <t>comp_concession</t>
+        </is>
+      </c>
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D187" s="7" t="inlineStr">
+        <is>
+          <t>Monthly value of the advertised concession.</t>
+        </is>
+      </c>
+      <c r="E187" s="6" t="inlineStr">
+        <is>
+          <t>Operator's own weekly rent scrape</t>
+        </is>
+      </c>
+      <c r="F187" s="7" t="inlineStr">
+        <is>
+          <t>Concession assumption</t>
+        </is>
+      </c>
+      <c r="G187" s="7" t="inlineStr">
+        <is>
+          <t>$45</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="6" t="inlineStr">
         <is>
-          <t>Demand</t>
+          <t>Comps</t>
         </is>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>demand_ring</t>
+          <t>comp_net_effective_rent</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D188" s="7" t="inlineStr">
         <is>
-          <t>Drive-ring the row describes: 1, 3, 5, or 10 miles, or the MSA.</t>
+          <t>Asking rent less the amortized concession. Stated on every row — a concession-blind comp set is the most common way a rent assumption goes wrong.</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -6760,296 +6784,296 @@
       </c>
       <c r="F188" s="7" t="inlineStr">
         <is>
-          <t>Market summary</t>
+          <t>Market rent evidence</t>
         </is>
       </c>
       <c r="G188" s="7" t="inlineStr">
         <is>
-          <t>1 mi</t>
+          <t>$1,405</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>Demand</t>
+          <t>Comps</t>
         </is>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>demand_population</t>
+          <t>comp_asking_psf</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D189" s="7" t="inlineStr">
         <is>
-          <t>Population in the ring.</t>
+          <t>Asking rent per square foot.</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
         <is>
-          <t>Public demographic data</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F189" s="7" t="inlineStr">
         <is>
-          <t>Market summary</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G189" s="7" t="inlineStr">
         <is>
-          <t>9,840</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="6" t="inlineStr">
         <is>
-          <t>Demand</t>
+          <t>Comps</t>
         </is>
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>demand_households</t>
+          <t>comp_occupancy</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D190" s="7" t="inlineStr">
         <is>
-          <t>Households in the ring.</t>
+          <t>Occupancy where the source published it.</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>Public demographic data</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F190" s="7" t="inlineStr">
         <is>
-          <t>Market summary</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G190" s="7" t="inlineStr">
         <is>
-          <t>4,020</t>
+          <t>94.0%</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>Demand</t>
+          <t>Comps</t>
         </is>
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>demand_median_income</t>
+          <t>comp_as_of</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D191" s="7" t="inlineStr">
         <is>
-          <t>Median household income in the ring.</t>
+          <t>When the row was scraped.</t>
         </is>
       </c>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t>Public demographic data</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F191" s="7" t="inlineStr">
         <is>
-          <t>Affordability check</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G191" s="7" t="inlineStr">
         <is>
-          <t>$78,400</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="6" t="inlineStr">
         <is>
-          <t>Demand</t>
+          <t>Comps</t>
         </is>
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>demand_jobs</t>
+          <t>comp_source</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D192" s="7" t="inlineStr">
         <is>
-          <t>Jobs located in the ring.</t>
+          <t>Always the operator's own weekly scrape. Licensed comp feeds are excluded by design and cannot be represented in this schema.</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>Public demographic data</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F192" s="7" t="inlineStr">
         <is>
-          <t>Market summary</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G192" s="7" t="inlineStr">
         <is>
-          <t>3,150</t>
+          <t>own weekly scrape</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>Demand</t>
+          <t>Comps</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>demand_pop_growth_5yr</t>
+          <t>compset_avg_asking</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D193" s="7" t="inlineStr">
         <is>
-          <t>Five-year population growth in the ring.</t>
+          <t>Average asking rent across the comp set.</t>
         </is>
       </c>
       <c r="E193" s="6" t="inlineStr">
         <is>
-          <t>Public demographic data</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F193" s="7" t="inlineStr">
         <is>
-          <t>Growth assumption evidence</t>
+          <t>Market rent benchmark</t>
         </is>
       </c>
       <c r="G193" s="7" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="6" t="inlineStr">
         <is>
+          <t>Comps</t>
+        </is>
+      </c>
+      <c r="B194" s="6" t="inlineStr">
+        <is>
+          <t>compset_avg_net_effective</t>
+        </is>
+      </c>
+      <c r="C194" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D194" s="7" t="inlineStr">
+        <is>
+          <t>Average net effective rent across the comp set.</t>
+        </is>
+      </c>
+      <c r="E194" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F194" s="7" t="inlineStr">
+        <is>
+          <t>Market rent benchmark</t>
+        </is>
+      </c>
+      <c r="G194" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="6" t="inlineStr">
+        <is>
+          <t>Comps</t>
+        </is>
+      </c>
+      <c r="B195" s="6" t="inlineStr">
+        <is>
+          <t>subject_vs_compset_spread</t>
+        </is>
+      </c>
+      <c r="C195" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D195" s="7" t="inlineStr">
+        <is>
+          <t>Subject market rent over comp-set net effective, less one.</t>
+        </is>
+      </c>
+      <c r="E195" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F195" s="7" t="inlineStr">
+        <is>
+          <t>Rent positioning</t>
+        </is>
+      </c>
+      <c r="G195" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="inlineStr">
+        <is>
           <t>Demand</t>
         </is>
       </c>
-      <c r="B194" s="6" t="inlineStr">
-        <is>
-          <t>demand_renter_share</t>
-        </is>
-      </c>
-      <c r="C194" s="6" t="inlineStr">
-        <is>
-          <t>percent</t>
-        </is>
-      </c>
-      <c r="D194" s="7" t="inlineStr">
-        <is>
-          <t>Share of ring households that rent.</t>
-        </is>
-      </c>
-      <c r="E194" s="6" t="inlineStr">
-        <is>
-          <t>Public demographic data</t>
-        </is>
-      </c>
-      <c r="F194" s="7" t="inlineStr">
-        <is>
-          <t>Demand context</t>
-        </is>
-      </c>
-      <c r="G194" s="7" t="inlineStr">
-        <is>
-          <t>44.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="5" t="inlineStr">
-        <is>
-          <t>Supply</t>
-        </is>
-      </c>
-      <c r="B195" s="5" t="n"/>
-      <c r="C195" s="5" t="n"/>
-      <c r="D195" s="5" t="n"/>
-      <c r="E195" s="5" t="n"/>
-      <c r="F195" s="5" t="n"/>
-      <c r="G195" s="5" t="n"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="6" t="inlineStr">
-        <is>
-          <t>Supply</t>
-        </is>
-      </c>
-      <c r="B196" s="6" t="inlineStr">
-        <is>
-          <t>supply_ring</t>
-        </is>
-      </c>
-      <c r="C196" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D196" s="7" t="inlineStr">
-        <is>
-          <t>Ring the supply row describes.</t>
-        </is>
-      </c>
-      <c r="E196" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F196" s="7" t="inlineStr">
-        <is>
-          <t>Competing supply</t>
-        </is>
-      </c>
-      <c r="G196" s="7" t="inlineStr">
-        <is>
-          <t>1 mi</t>
-        </is>
-      </c>
+      <c r="B196" s="5" t="n"/>
+      <c r="C196" s="5" t="n"/>
+      <c r="D196" s="5" t="n"/>
+      <c r="E196" s="5" t="n"/>
+      <c r="F196" s="5" t="n"/>
+      <c r="G196" s="5" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>Supply</t>
+          <t>Demand</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>supply_stage</t>
+          <t>demand_ring</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
@@ -7059,34 +7083,34 @@
       </c>
       <c r="D197" s="7" t="inlineStr">
         <is>
-          <t>Entitlement, permitted, under construction, or delivered in the last 24 months. Stage is stated because entitled units and delivered units are not the same risk.</t>
+          <t>Drive-ring the row describes: 1, 3, 5, or 10 miles, or the MSA.</t>
         </is>
       </c>
       <c r="E197" s="6" t="inlineStr">
         <is>
-          <t>Public permit / entitlement records</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F197" s="7" t="inlineStr">
         <is>
-          <t>Competing supply</t>
+          <t>Market summary</t>
         </is>
       </c>
       <c r="G197" s="7" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>1 mi</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>Supply</t>
+          <t>Demand</t>
         </is>
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>supply_projects</t>
+          <t>demand_population</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">
@@ -7096,34 +7120,34 @@
       </c>
       <c r="D198" s="7" t="inlineStr">
         <is>
-          <t>Projects at that ring and stage.</t>
+          <t>Population in the ring.</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
         <is>
-          <t>Public permit / entitlement records</t>
+          <t>Public demographic data</t>
         </is>
       </c>
       <c r="F198" s="7" t="inlineStr">
         <is>
-          <t>Competing supply</t>
+          <t>Market summary</t>
         </is>
       </c>
       <c r="G198" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9,840</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>Supply</t>
+          <t>Demand</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>supply_units</t>
+          <t>demand_households</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
@@ -7133,94 +7157,403 @@
       </c>
       <c r="D199" s="7" t="inlineStr">
         <is>
-          <t>Units at that ring and stage.</t>
+          <t>Households in the ring.</t>
         </is>
       </c>
       <c r="E199" s="6" t="inlineStr">
         <is>
-          <t>Public permit / entitlement records</t>
+          <t>Public demographic data</t>
         </is>
       </c>
       <c r="F199" s="7" t="inlineStr">
         <is>
-          <t>Competing supply / absorption</t>
+          <t>Market summary</t>
         </is>
       </c>
       <c r="G199" s="7" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>4,020</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="6" t="inlineStr">
         <is>
-          <t>Supply</t>
+          <t>Demand</t>
         </is>
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>supply_ring_total_units</t>
+          <t>demand_median_income</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D200" s="7" t="inlineStr">
         <is>
-          <t>All pipeline units in the ring across stages.</t>
+          <t>Median household income in the ring.</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Public demographic data</t>
         </is>
       </c>
       <c r="F200" s="7" t="inlineStr">
         <is>
-          <t>Competing supply</t>
+          <t>Affordability check</t>
         </is>
       </c>
       <c r="G200" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$78,400</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
         <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B201" s="6" t="inlineStr">
+        <is>
+          <t>demand_jobs</t>
+        </is>
+      </c>
+      <c r="C201" s="6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D201" s="7" t="inlineStr">
+        <is>
+          <t>Jobs located in the ring.</t>
+        </is>
+      </c>
+      <c r="E201" s="6" t="inlineStr">
+        <is>
+          <t>Public demographic data</t>
+        </is>
+      </c>
+      <c r="F201" s="7" t="inlineStr">
+        <is>
+          <t>Market summary</t>
+        </is>
+      </c>
+      <c r="G201" s="7" t="inlineStr">
+        <is>
+          <t>3,150</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="6" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B202" s="6" t="inlineStr">
+        <is>
+          <t>demand_pop_growth_5yr</t>
+        </is>
+      </c>
+      <c r="C202" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D202" s="7" t="inlineStr">
+        <is>
+          <t>Five-year population growth in the ring.</t>
+        </is>
+      </c>
+      <c r="E202" s="6" t="inlineStr">
+        <is>
+          <t>Public demographic data</t>
+        </is>
+      </c>
+      <c r="F202" s="7" t="inlineStr">
+        <is>
+          <t>Growth assumption evidence</t>
+        </is>
+      </c>
+      <c r="G202" s="7" t="inlineStr">
+        <is>
+          <t>6.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="6" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B203" s="6" t="inlineStr">
+        <is>
+          <t>demand_renter_share</t>
+        </is>
+      </c>
+      <c r="C203" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D203" s="7" t="inlineStr">
+        <is>
+          <t>Share of ring households that rent.</t>
+        </is>
+      </c>
+      <c r="E203" s="6" t="inlineStr">
+        <is>
+          <t>Public demographic data</t>
+        </is>
+      </c>
+      <c r="F203" s="7" t="inlineStr">
+        <is>
+          <t>Demand context</t>
+        </is>
+      </c>
+      <c r="G203" s="7" t="inlineStr">
+        <is>
+          <t>44.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="inlineStr">
+        <is>
           <t>Supply</t>
         </is>
       </c>
-      <c r="B201" s="6" t="inlineStr">
+      <c r="B204" s="5" t="n"/>
+      <c r="C204" s="5" t="n"/>
+      <c r="D204" s="5" t="n"/>
+      <c r="E204" s="5" t="n"/>
+      <c r="F204" s="5" t="n"/>
+      <c r="G204" s="5" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="6" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B205" s="6" t="inlineStr">
+        <is>
+          <t>supply_ring</t>
+        </is>
+      </c>
+      <c r="C205" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D205" s="7" t="inlineStr">
+        <is>
+          <t>Ring the supply row describes.</t>
+        </is>
+      </c>
+      <c r="E205" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F205" s="7" t="inlineStr">
+        <is>
+          <t>Competing supply</t>
+        </is>
+      </c>
+      <c r="G205" s="7" t="inlineStr">
+        <is>
+          <t>1 mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="6" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B206" s="6" t="inlineStr">
+        <is>
+          <t>supply_stage</t>
+        </is>
+      </c>
+      <c r="C206" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D206" s="7" t="inlineStr">
+        <is>
+          <t>Entitlement, permitted, under construction, or delivered in the last 24 months. Stage is stated because entitled units and delivered units are not the same risk.</t>
+        </is>
+      </c>
+      <c r="E206" s="6" t="inlineStr">
+        <is>
+          <t>Public permit / entitlement records</t>
+        </is>
+      </c>
+      <c r="F206" s="7" t="inlineStr">
+        <is>
+          <t>Competing supply</t>
+        </is>
+      </c>
+      <c r="G206" s="7" t="inlineStr">
+        <is>
+          <t>Entitlement</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="6" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B207" s="6" t="inlineStr">
+        <is>
+          <t>supply_projects</t>
+        </is>
+      </c>
+      <c r="C207" s="6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D207" s="7" t="inlineStr">
+        <is>
+          <t>Projects at that ring and stage.</t>
+        </is>
+      </c>
+      <c r="E207" s="6" t="inlineStr">
+        <is>
+          <t>Public permit / entitlement records</t>
+        </is>
+      </c>
+      <c r="F207" s="7" t="inlineStr">
+        <is>
+          <t>Competing supply</t>
+        </is>
+      </c>
+      <c r="G207" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="6" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B208" s="6" t="inlineStr">
+        <is>
+          <t>supply_units</t>
+        </is>
+      </c>
+      <c r="C208" s="6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D208" s="7" t="inlineStr">
+        <is>
+          <t>Units at that ring and stage.</t>
+        </is>
+      </c>
+      <c r="E208" s="6" t="inlineStr">
+        <is>
+          <t>Public permit / entitlement records</t>
+        </is>
+      </c>
+      <c r="F208" s="7" t="inlineStr">
+        <is>
+          <t>Competing supply / absorption</t>
+        </is>
+      </c>
+      <c r="G208" s="7" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="6" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B209" s="6" t="inlineStr">
+        <is>
+          <t>supply_ring_total_units</t>
+        </is>
+      </c>
+      <c r="C209" s="6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D209" s="7" t="inlineStr">
+        <is>
+          <t>All pipeline units in the ring across stages.</t>
+        </is>
+      </c>
+      <c r="E209" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F209" s="7" t="inlineStr">
+        <is>
+          <t>Competing supply</t>
+        </is>
+      </c>
+      <c r="G209" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="6" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B210" s="6" t="inlineStr">
         <is>
           <t>supply_pct_of_ring_stock</t>
         </is>
       </c>
-      <c r="C201" s="6" t="inlineStr">
+      <c r="C210" s="6" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="D201" s="7" t="inlineStr">
+      <c r="D210" s="7" t="inlineStr">
         <is>
           <t>Pipeline units as a share of the ring's existing stock, where stock is known.</t>
         </is>
       </c>
-      <c r="E201" s="6" t="inlineStr">
+      <c r="E210" s="6" t="inlineStr">
         <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="F201" s="7" t="inlineStr">
+      <c r="F210" s="7" t="inlineStr">
         <is>
           <t>Supply pressure</t>
         </is>
       </c>
-      <c r="G201" s="7" t="inlineStr">
+      <c r="G210" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7237,7 +7570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -7287,7 +7620,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -7298,7 +7631,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50/50 (100%)</t>
+          <t>52/52 (100%)</t>
         </is>
       </c>
     </row>
@@ -7416,50 +7749,54 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>comps.rows</t>
+          <t>comps.nearby</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>10 entries</t>
+          <t>4 entries</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Synthetic weekly rent scrape</t>
+          <t>Tracked-community registry</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>rents.communities within the radius</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>comps.rows.tier</t>
+        </is>
+      </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Own weekly scrape; asking and net effective stated separately.</t>
+          <t>Every tracked community inside the radius that is not a detail row, with the reason it is not. No rent columns.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>demand.rings</t>
+          <t>comps.rows</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>5 entries</t>
+          <t>25 entries</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Synthetic public data extract</t>
+          <t>Synthetic weekly rent scrape</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -7475,95 +7812,99 @@
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Ring demographics.</t>
+          <t>Own weekly scrape; asking and net effective stated separately.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>pricing.price_per_unit</t>
+          <t>comps.rows.tier</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>215,000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Tracked-community registry + the scrape</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>comp_tiers.assign</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>comps.rows.distance_mi, comps.tiering.subject_product, comps.tiering.subject_year_built, comps.tiering.year_band, comps.tiering.top_n, comps.tiering.additional_n</t>
+        </is>
+      </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Illustrative. Inside the band a per-unit sale price occupies.</t>
+          <t>Tier 1 = the closest 5 matching product and vintage; tier 2 = the next 15; everything else is tier 3, identity only. An unknown year does not disqualify — it is disclosed on the tier header instead.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>pricing.unit_count</t>
+          <t>demand.rings</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>5 entries</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Synthetic rent roll export</t>
+          <t>Synthetic public data extract</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Rent Roll!A:A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>summary.unit_count</t>
-        </is>
-      </c>
-      <c r="G14" s="13" t="n"/>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Ring demographics.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>rent_roll.as_of</t>
+          <t>pricing.price_per_unit</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>215,000</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Synthetic rent roll export</t>
+          <t>Supplied by the operator</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Rent Roll!A2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -7572,60 +7913,64 @@
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
-      <c r="G15" s="13" t="n"/>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Illustrative. Inside the band a per-unit sale price occupies.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>rent_roll.lookback_months</t>
+          <t>pricing.unit_count</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>180</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Synthetic rent roll export</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rent Roll!A:A</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>Analysis knob.</t>
-        </is>
-      </c>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>summary.unit_count</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>rent_roll.new_tenant_tolerance_days</t>
+          <t>rent_roll.as_of</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Synthetic rent roll export</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rent Roll!A2</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -7634,31 +7979,27 @@
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>Analysis knob.</t>
-        </is>
-      </c>
+      <c r="G17" s="13" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>rent_roll.units</t>
+          <t>rent_roll.lookback_months</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>180 entries</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Synthetic rent roll export</t>
+          <t>Supplied by the operator</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Rent Roll!A4:K183</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -7669,29 +8010,29 @@
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Unit identifiers only; the source's resident-name column is never read.</t>
+          <t>Analysis knob.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>summary.assessed_value_basis</t>
+          <t>rent_roll.new_tenant_tolerance_days</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>23,000,000</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Synthetic county tax record</t>
+          <t>Supplied by the operator</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Valuation notice</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -7700,27 +8041,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
-      <c r="G19" s="13" t="n"/>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Analysis knob.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>summary.assessment_ratio</t>
+          <t>rent_roll.units</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>180 entries</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Synthetic county tax record</t>
+          <t>Synthetic rent roll export</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Rate table</t>
+          <t>Rent Roll!A4:K183</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -7729,27 +8074,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
-      <c r="G20" s="13" t="n"/>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Unit identifiers only; the source's resident-name column is never read.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>summary.city</t>
+          <t>summary.assessed_value_basis</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Sample City</t>
+          <t>23,000,000</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Synthetic county tax record</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>p.4</t>
+          <t>Valuation notice</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -7763,22 +8112,22 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>summary.construction_status</t>
+          <t>summary.assessment_ratio</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Stabilized</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Synthetic county tax record</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>p.6</t>
+          <t>Rate table</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -7792,12 +8141,12 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>summary.county</t>
+          <t>summary.city</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Example County</t>
+          <t>Sample City</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -7821,12 +8170,12 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>summary.deal_name</t>
+          <t>summary.construction_status</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Fixture Park</t>
+          <t>Stabilized</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -7836,7 +8185,7 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>p.1</t>
+          <t>p.6</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -7845,21 +8194,17 @@
         </is>
       </c>
       <c r="F24" s="12" t="n"/>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>Fixture Park</t>
-        </is>
-      </c>
+      <c r="G24" s="13" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>summary.deal_status</t>
+          <t>summary.county</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>On the market</t>
+          <t>Example County</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -7869,7 +8214,7 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>p.2</t>
+          <t>p.4</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -7883,12 +8228,12 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>summary.delivery_date</t>
+          <t>summary.deal_name</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Delivered 2019; fully stabilized since 2021</t>
+          <t>Fixture Park</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -7898,7 +8243,7 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>p.6</t>
+          <t>p.1</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -7907,27 +8252,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n"/>
-      <c r="G26" s="13" t="n"/>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Fixture Park</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>summary.fair_market_value</t>
+          <t>summary.deal_status</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>39,600,000</t>
+          <t>On the market</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Synthetic offering memorandum</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.2</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -7936,63 +8285,51 @@
         </is>
       </c>
       <c r="F27" s="12" t="n"/>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>Operator's own estimate.</t>
-        </is>
-      </c>
+      <c r="G27" s="13" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>summary.in_place_rent_avg</t>
+          <t>summary.delivery_date</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>1,795.36</t>
+          <t>Delivered 2019; fully stabilized since 2021</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Synthetic offering memorandum</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Unit Mix Summary!E</t>
+          <t>p.6</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>computed</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>rent_roll.units</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>Occupied units, straight off the roll.</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="n"/>
+      <c r="G28" s="13" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>summary.listing_brokerage</t>
+          <t>summary.fair_market_value</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Listing brokerage</t>
+          <t>39,600,000</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Supplied by the operator</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -8002,29 +8339,25 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>summary.seller_entity</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n"/>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Generic label; no firm or individual is named in a published file.</t>
+          <t>Operator's own estimate.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>summary.market_rent_for_model</t>
+          <t>summary.in_place_rent_avg</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>1,834.78</t>
+          <t>1,795.36</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -8034,7 +8367,7 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Unit Mix Summary!H</t>
+          <t>Unit Mix Summary!E</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -8049,19 +8382,19 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>New-lease average where a plan has new leases in the window, else in-place. Never a blend.</t>
+          <t>Occupied units, straight off the roll.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>summary.msa</t>
+          <t>summary.listing_brokerage</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Sample City MSA</t>
+          <t>Listing brokerage</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -8081,96 +8414,108 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>summary.city, summary.state</t>
+          <t>summary.seller_entity</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Metro assigned from the city/state pair.</t>
+          <t>Generic label; no firm or individual is named in a published file.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>summary.pricing_guidance</t>
+          <t>summary.market_rent_for_model</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>$215,000 per unit (illustrative)</t>
+          <t>1,834.78</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Unit Mix Summary!H</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F32" s="12" t="n"/>
+          <t>computed</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>Illustrative figure supplied directly; not a quote or an offer.</t>
+          <t>New-lease average where a plan has new leases in the window, else in-place. Never a blend.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>summary.product_detail</t>
+          <t>summary.msa</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>180 units across six plans: 62 one-bedroom (720–795 SF), 78 two-bedroom (1,050–1,140 SF…</t>
+          <t>Sample City MSA</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>p.7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="n"/>
-      <c r="G33" s="13" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>summary.city, summary.state</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Metro assigned from the city/state pair.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>summary.product_type</t>
+          <t>summary.pricing_guidance</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>MF</t>
+          <t>$215,000 per unit (illustrative)</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Supplied by the operator</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>p.6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -8179,27 +8524,31 @@
         </is>
       </c>
       <c r="F34" s="12" t="n"/>
-      <c r="G34" s="13" t="n"/>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>Illustrative figure supplied directly; not a quote or an offer.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>summary.school_elementary_name</t>
+          <t>summary.product_detail</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Example Creek Elementary</t>
+          <t>180 units across six plans: 62 one-bedroom (720–795 SF), 78 two-bedroom (1,050–1,140 SF…</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Synthetic public data extract</t>
+          <t>Synthetic offering memorandum</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>School attendance lookup</t>
+          <t>p.7</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -8213,22 +8562,22 @@
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>summary.school_high_name</t>
+          <t>summary.product_type</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Sample City High</t>
+          <t>MF</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Synthetic public data extract</t>
+          <t>Synthetic offering memorandum</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>School attendance lookup</t>
+          <t>p.6</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -8242,12 +8591,12 @@
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>summary.school_middle_name</t>
+          <t>summary.school_elementary_name</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Example Ridge Middle</t>
+          <t>Example Creek Elementary</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -8271,22 +8620,22 @@
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>summary.seller_entity</t>
+          <t>summary.school_high_name</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Sample City Residential Holdings LLC</t>
+          <t>Sample City High</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Synthetic public data extract</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>p.2</t>
+          <t>School attendance lookup</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -8300,22 +8649,22 @@
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>summary.state</t>
+          <t>summary.school_middle_name</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>Example Ridge Middle</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Synthetic public data extract</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>p.4</t>
+          <t>School attendance lookup</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -8329,12 +8678,12 @@
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>summary.street_address</t>
+          <t>summary.seller_entity</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>1400 Example Parkway</t>
+          <t>Sample City Residential Holdings LLC</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -8344,7 +8693,7 @@
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>p.4</t>
+          <t>p.2</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -8353,21 +8702,17 @@
         </is>
       </c>
       <c r="F40" s="12" t="n"/>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>1400 Example Parkway</t>
-        </is>
-      </c>
+      <c r="G40" s="13" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>summary.structure</t>
+          <t>summary.state</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Three-story garden, surface parked</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -8377,7 +8722,7 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>p.6</t>
+          <t>p.4</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -8386,31 +8731,27 @@
         </is>
       </c>
       <c r="F41" s="12" t="n"/>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>Three-story garden, surface parked</t>
-        </is>
-      </c>
+      <c r="G41" s="13" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_area_code</t>
+          <t>summary.street_address</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>SYN-0000</t>
+          <t>1400 Example Parkway</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Synthetic county tax record</t>
+          <t>Synthetic offering memorandum</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Rate table</t>
+          <t>p.4</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -8419,27 +8760,31 @@
         </is>
       </c>
       <c r="F42" s="12" t="n"/>
-      <c r="G42" s="13" t="n"/>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>1400 Example Parkway</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_basis_label</t>
+          <t>summary.structure</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Assessed value (synthetic)</t>
+          <t>Three-story garden, surface parked</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Synthetic county tax record</t>
+          <t>Synthetic offering memorandum</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Valuation notice</t>
+          <t>p.6</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -8448,17 +8793,21 @@
         </is>
       </c>
       <c r="F43" s="12" t="n"/>
-      <c r="G43" s="13" t="n"/>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Three-story garden, surface parked</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_basis_note</t>
+          <t>summary.tax_area_code</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Synthetic basis. On a real deal this row states what the basis IS in that state and whe…</t>
+          <t>SYN-0000</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -8468,7 +8817,7 @@
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Valuation notice</t>
+          <t>Rate table</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -8482,12 +8831,12 @@
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_billed_amount</t>
+          <t>summary.tax_basis_label</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>494,040</t>
+          <t>Assessed value (synthetic)</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -8497,7 +8846,7 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Tax bill</t>
+          <t>Valuation notice</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -8511,12 +8860,12 @@
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_billed_year</t>
+          <t>summary.tax_basis_note</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>2,025</t>
+          <t>Synthetic basis. On a real deal this row states what the basis IS in that state and whe…</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -8526,7 +8875,7 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Tax bill</t>
+          <t>Valuation notice</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -8540,12 +8889,12 @@
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_divisor</t>
+          <t>summary.tax_billed_amount</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>494,040</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -8555,7 +8904,7 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Rate table</t>
+          <t>Tax bill</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -8569,12 +8918,12 @@
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_exemption</t>
+          <t>summary.tax_billed_year</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2,025</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -8584,7 +8933,7 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Valuation notice</t>
+          <t>Tax bill</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -8598,12 +8947,12 @@
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_parcel_id</t>
+          <t>summary.tax_divisor</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>SYN-000-00-000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -8613,7 +8962,7 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Parcel record</t>
+          <t>Rate table</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -8627,12 +8976,12 @@
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_rate_as_billed</t>
+          <t>summary.tax_exemption</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -8642,7 +8991,7 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Rate table, synthetic district</t>
+          <t>Valuation notice</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -8656,59 +9005,51 @@
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>summary.unit_count</t>
+          <t>summary.tax_parcel_id</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>SYN-000-00-000</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Synthetic rent roll export</t>
+          <t>Synthetic county tax record</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Rent Roll!A:A</t>
+          <t>Parcel record</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>rent_roll.units</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>Distinct unit identifiers on the roll.</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n"/>
+      <c r="G51" s="13" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>summary.year_built</t>
+          <t>summary.tax_rate_as_billed</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>2,019</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Synthetic county tax record</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>p.6</t>
+          <t>Rate table, synthetic district</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -8722,51 +9063,59 @@
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>summary.zip</t>
+          <t>summary.unit_count</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>180</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Synthetic rent roll export</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>p.4</t>
+          <t>Rent Roll!A:A</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F53" s="12" t="n"/>
-      <c r="G53" s="13" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Distinct unit identifiers on the roll.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>supply.rings</t>
+          <t>summary.year_built</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>12 entries</t>
+          <t>2,019</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Synthetic public data extract</t>
+          <t>Synthetic offering memorandum</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.6</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -8775,31 +9124,27 @@
         </is>
       </c>
       <c r="F54" s="12" t="n"/>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>Permit and entitlement records.</t>
-        </is>
-      </c>
+      <c r="G54" s="13" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>t12.month_labels</t>
+          <t>summary.zip</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>12 entries</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Synthetic trailing-twelve income statement</t>
+          <t>Synthetic offering memorandum</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>T-12!C8:N8</t>
+          <t>p.4</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -8808,31 +9153,27 @@
         </is>
       </c>
       <c r="F55" s="12" t="n"/>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>Twelve consecutive month-end columns; direction detected from the labels.</t>
-        </is>
-      </c>
+      <c r="G55" s="13" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>t12.source_subtotals</t>
+          <t>supply.rings</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>5 keys</t>
+          <t>12 entries</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Synthetic trailing-twelve income statement</t>
+          <t>Synthetic public data extract</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>T-12!O</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -8843,62 +9184,62 @@
       <c r="F56" s="12" t="n"/>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>The statement's own printed subtotals, kept for the cross-tie.</t>
+          <t>Permit and entitlement records.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>t12.units</t>
+          <t>t12.month_labels</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>12 entries</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Synthetic rent roll export</t>
+          <t>Synthetic trailing-twelve income statement</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-12!C8:N8</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>summary.unit_count</t>
-        </is>
-      </c>
-      <c r="G57" s="13" t="n"/>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="n"/>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>Twelve consecutive month-end columns; direction detected from the labels.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>trade_out.rows</t>
+          <t>t12.source_subtotals</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>3 entries</t>
+          <t>5 keys</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Synthetic lease trade-out report</t>
+          <t>Synthetic trailing-twelve income statement</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-12!O</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -8908,6 +9249,72 @@
       </c>
       <c r="F58" s="12" t="n"/>
       <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>The statement's own printed subtotals, kept for the cross-tie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>t12.units</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic rent roll export</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>summary.unit_count</t>
+        </is>
+      </c>
+      <c r="G59" s="13" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>trade_out.rows</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>3 entries</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic lease trade-out report</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="n"/>
+      <c r="G60" s="7" t="inlineStr">
         <is>
           <t>Cohort averages.</t>
         </is>

--- a/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
+++ b/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
@@ -3158,7 +3158,7 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Gain/(Loss) to Lease</t>
+          <t>Gain / (Loss) to Lease</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Gain/(Loss) to Lease — trailing-twelve total, and trailing-three annualized beside it.</t>
+          <t>Gain / (Loss) to Lease — trailing-twelve total, and trailing-three annualized beside it.</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>G&amp;A</t>
+          <t>General and Administrative</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>G&amp;A — trailing-twelve total, trailing-three annualized, and per unit.</t>
+          <t>General and Administrative — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">

--- a/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
+++ b/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G210"/>
+  <dimension ref="A1:G212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7">
@@ -4620,54 +4620,54 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="inlineStr">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>T-12 structure</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>absent_reason</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>Why the T-12 section is empty, when no trailing-twelve statement was supplied. Twelve months of zeroes would validate and read as a property that earned nothing; a stated reason cannot be mistaken for one.</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>Rent roll — unit</t>
         </is>
       </c>
-      <c r="B127" s="5" t="n"/>
-      <c r="C127" s="5" t="n"/>
-      <c r="D127" s="5" t="n"/>
-      <c r="E127" s="5" t="n"/>
-      <c r="F127" s="5" t="n"/>
-      <c r="G127" s="5" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>Rent roll — unit</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>unit_id</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D128" s="7" t="inlineStr">
-        <is>
-          <t>Unit identifier. The output carries unit IDs only; no tenant-name column exists in the schema.</t>
-        </is>
-      </c>
-      <c r="E128" s="6" t="inlineStr">
-        <is>
-          <t>Rent roll export</t>
-        </is>
-      </c>
-      <c r="F128" s="7" t="inlineStr">
-        <is>
-          <t>Unit list</t>
-        </is>
-      </c>
-      <c r="G128" s="7" t="inlineStr">
-        <is>
-          <t>A1-101</t>
-        </is>
-      </c>
+      <c r="B128" s="5" t="n"/>
+      <c r="C128" s="5" t="n"/>
+      <c r="D128" s="5" t="n"/>
+      <c r="E128" s="5" t="n"/>
+      <c r="F128" s="5" t="n"/>
+      <c r="G128" s="5" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>floor_plan</t>
+          <t>unit_id</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>Floor-plan code the unit belongs to.</t>
+          <t>Unit identifier. The output carries unit IDs only; no tenant-name column exists in the schema.</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>Unit mix</t>
+          <t>Unit list</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-101</t>
         </is>
       </c>
     </row>
@@ -4714,17 +4714,17 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>beds</t>
+          <t>floor_plan</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>Bedrooms.</t>
+          <t>Floor-plan code the unit belongs to.</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>A1</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>baths</t>
+          <t>beds</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>Bathrooms.</t>
+          <t>Bedrooms.</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>sqft</t>
+          <t>baths</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>Square footage.</t>
+          <t>Bathrooms.</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -4825,17 +4825,17 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>sqft</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Occupied, vacant, or model/down.</t>
+          <t>Square footage.</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
@@ -4845,12 +4845,12 @@
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Unit mix</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>Occupied</t>
+          <t>720</t>
         </is>
       </c>
     </row>
@@ -4862,17 +4862,17 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>lease_start</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>Lease start. A value the source gave as text stays text — a date that arrives as 'n/a' is not coerced into 1899.</t>
+          <t>Occupied, vacant, or model/down.</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -4882,12 +4882,12 @@
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>Occupied</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>move_in</t>
+          <t>lease_start</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Move-in date. Turnover is counted by move-in, not by lease start.</t>
+          <t>Lease start. A value the source gave as text stays text — a date that arrives as 'n/a' is not coerced into 1899.</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Turnover</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
@@ -4936,32 +4936,32 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>lease_type</t>
+          <t>move_in</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>New, Renewal, or blank. Blank means the source could not support a classification — never a guess, never a blend.</t>
+          <t>Move-in date. Turnover is counted by move-in, not by lease start.</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Rent roll export</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>New-vs-renewal split</t>
+          <t>Turnover</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>2025-07-03</t>
         </is>
       </c>
     </row>
@@ -4973,32 +4973,32 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>in_place_rent</t>
+          <t>lease_type</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>Contract rent in place.</t>
+          <t>New, Renewal, or blank. Blank means the source could not support a classification — never a guess, never a blend.</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>Rent roll export</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>In-place rent</t>
+          <t>New-vs-renewal split</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
         <is>
-          <t>$1,535</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -5010,84 +5010,84 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
+          <t>in_place_rent</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D138" s="7" t="inlineStr">
+        <is>
+          <t>Contract rent in place.</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll export</t>
+        </is>
+      </c>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t>In-place rent</t>
+        </is>
+      </c>
+      <c r="G138" s="7" t="inlineStr">
+        <is>
+          <t>$1,535</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll — unit</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
           <t>rent_per_sf</t>
         </is>
       </c>
-      <c r="C138" s="6" t="inlineStr">
+      <c r="C139" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D138" s="7" t="inlineStr">
+      <c r="D139" s="7" t="inlineStr">
         <is>
           <t>In-place rent divided by square footage.</t>
         </is>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="E139" s="6" t="inlineStr">
         <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="F138" s="7" t="inlineStr">
+      <c r="F139" s="7" t="inlineStr">
         <is>
           <t>Rent per square foot</t>
         </is>
       </c>
-      <c r="G138" s="7" t="inlineStr">
+      <c r="G139" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="5" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
         <is>
           <t>Rent roll — plan</t>
         </is>
       </c>
-      <c r="B139" s="5" t="n"/>
-      <c r="C139" s="5" t="n"/>
-      <c r="D139" s="5" t="n"/>
-      <c r="E139" s="5" t="n"/>
-      <c r="F139" s="5" t="n"/>
-      <c r="G139" s="5" t="n"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="6" t="inlineStr">
-        <is>
-          <t>Rent roll — plan</t>
-        </is>
-      </c>
-      <c r="B140" s="6" t="inlineStr">
-        <is>
-          <t>plan_avg_sqft</t>
-        </is>
-      </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="D140" s="7" t="inlineStr">
-        <is>
-          <t>Average square footage for the plan.</t>
-        </is>
-      </c>
-      <c r="E140" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F140" s="7" t="inlineStr">
-        <is>
-          <t>Unit mix — average SF</t>
-        </is>
-      </c>
-      <c r="G140" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B140" s="5" t="n"/>
+      <c r="C140" s="5" t="n"/>
+      <c r="D140" s="5" t="n"/>
+      <c r="E140" s="5" t="n"/>
+      <c r="F140" s="5" t="n"/>
+      <c r="G140" s="5" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
@@ -5097,17 +5097,17 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>plan_units</t>
+          <t>plan_avg_sqft</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>Units in the plan.</t>
+          <t>Average square footage for the plan.</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>Unit mix — count</t>
+          <t>Unit mix — average SF</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>plan_occupied</t>
+          <t>plan_units</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>Occupied units in the plan.</t>
+          <t>Units in the plan.</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>Occupancy by plan</t>
+          <t>Unit mix — count</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>plan_vacant</t>
+          <t>plan_occupied</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>Vacant units in the plan.</t>
+          <t>Occupied units in the plan.</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>plan_avg_in_place_rent</t>
+          <t>plan_vacant</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>Weighted average in-place rent for the plan's occupied units.</t>
+          <t>Vacant units in the plan.</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>In-place rent by plan</t>
+          <t>Occupancy by plan</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>plan_new_lease_rent</t>
+          <t>plan_avg_in_place_rent</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>Average rent on the plan's new leases inside the lookback window. Renewals are excluded.</t>
+          <t>Weighted average in-place rent for the plan's occupied units.</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>New-lease rent evidence</t>
+          <t>In-place rent by plan</t>
         </is>
       </c>
       <c r="G145" s="7" t="inlineStr">
@@ -5282,17 +5282,17 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>plan_new_lease_count</t>
+          <t>plan_new_lease_rent</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>How many new leases the average rests on. A thin count is visible rather than implied.</t>
+          <t>Average rent on the plan's new leases inside the lookback window. Renewals are excluded.</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>Sample size</t>
+          <t>New-lease rent evidence</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr">
@@ -5319,17 +5319,17 @@
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>plan_market_rent_for_model</t>
+          <t>plan_new_lease_count</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>The plan's rent to underwrite: new-lease average where one exists, otherwise in-place. This is the column a financial model consumes.</t>
+          <t>How many new leases the average rests on. A thin count is visible rather than implied.</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>Unit-mix market rent</t>
+          <t>Sample size</t>
         </is>
       </c>
       <c r="G147" s="7" t="inlineStr">
@@ -5356,84 +5356,84 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
+          <t>plan_market_rent_for_model</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>The plan's rent to underwrite: new-lease average where one exists, otherwise in-place. This is the column a financial model consumes.</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F148" s="7" t="inlineStr">
+        <is>
+          <t>Unit-mix market rent</t>
+        </is>
+      </c>
+      <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll — plan</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
           <t>plan_market_rent_basis</t>
         </is>
       </c>
-      <c r="C148" s="6" t="inlineStr">
+      <c r="C149" s="6" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D148" s="7" t="inlineStr">
+      <c r="D149" s="7" t="inlineStr">
         <is>
           <t>Which of the two fired, stated per plan.</t>
         </is>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="E149" s="6" t="inlineStr">
         <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="F148" s="7" t="inlineStr">
+      <c r="F149" s="7" t="inlineStr">
         <is>
           <t>Reference only — not a model input</t>
         </is>
       </c>
-      <c r="G148" s="7" t="inlineStr">
+      <c r="G149" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="5" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
         <is>
           <t>Rent roll — totals</t>
         </is>
       </c>
-      <c r="B149" s="5" t="n"/>
-      <c r="C149" s="5" t="n"/>
-      <c r="D149" s="5" t="n"/>
-      <c r="E149" s="5" t="n"/>
-      <c r="F149" s="5" t="n"/>
-      <c r="G149" s="5" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="6" t="inlineStr">
-        <is>
-          <t>Rent roll — totals</t>
-        </is>
-      </c>
-      <c r="B150" s="6" t="inlineStr">
-        <is>
-          <t>total_units</t>
-        </is>
-      </c>
-      <c r="C150" s="6" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D150" s="7" t="inlineStr">
-        <is>
-          <t>Units on the roll.</t>
-        </is>
-      </c>
-      <c r="E150" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F150" s="7" t="inlineStr">
-        <is>
-          <t>Unit count cross-check</t>
-        </is>
-      </c>
-      <c r="G150" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B150" s="5" t="n"/>
+      <c r="C150" s="5" t="n"/>
+      <c r="D150" s="5" t="n"/>
+      <c r="E150" s="5" t="n"/>
+      <c r="F150" s="5" t="n"/>
+      <c r="G150" s="5" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>occupied_units</t>
+          <t>total_units</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>Occupied units.</t>
+          <t>Units on the roll.</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Unit count cross-check</t>
         </is>
       </c>
       <c r="G151" s="7" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>vacant_units</t>
+          <t>occupied_units</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>Vacant units.</t>
+          <t>Occupied units.</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -5517,17 +5517,17 @@
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>occupancy</t>
+          <t>vacant_units</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>Occupied over total.</t>
+          <t>Vacant units.</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="F153" s="7" t="inlineStr">
         <is>
-          <t>Vacancy assumption</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="G153" s="7" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>vacancy</t>
+          <t>occupancy</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>One less occupancy. The physical-vacancy input.</t>
+          <t>Occupied over total.</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
@@ -5591,17 +5591,17 @@
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>wavg_in_place_rent</t>
+          <t>vacancy</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>Unit-weighted in-place rent across the property.</t>
+          <t>One less occupancy. The physical-vacancy input.</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="F155" s="7" t="inlineStr">
         <is>
-          <t>In-place rent</t>
+          <t>Vacancy assumption</t>
         </is>
       </c>
       <c r="G155" s="7" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>wavg_market_rent_for_model</t>
+          <t>wavg_in_place_rent</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>Unit-weighted market rent for model across the property.</t>
+          <t>Unit-weighted in-place rent across the property.</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>Market rent</t>
+          <t>In-place rent</t>
         </is>
       </c>
       <c r="G156" s="7" t="inlineStr">
@@ -5665,17 +5665,17 @@
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>annualized_turnover</t>
+          <t>wavg_market_rent_for_model</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>Move-ins inside the lookback window, annualized against unit count.</t>
+          <t>Unit-weighted market rent for model across the property.</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
-          <t>Turnover assumption</t>
+          <t>Market rent</t>
         </is>
       </c>
       <c r="G157" s="7" t="inlineStr">
@@ -5702,32 +5702,32 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>lookback_months</t>
+          <t>annualized_turnover</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>Length of the new-lease window, measured back from the roll's as-of date.</t>
+          <t>Move-ins inside the lookback window, annualized against unit count.</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F158" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Turnover assumption</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5739,7 +5739,7 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>new_tenant_tolerance_days</t>
+          <t>lookback_months</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>How far lease start may sit from move-in before a lease stops counting as a new tenant. A knob on the output, not a constant buried in code.</t>
+          <t>Length of the new-lease window, measured back from the roll's as-of date.</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="G159" s="7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -5776,121 +5776,121 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>roll_as_of</t>
+          <t>new_tenant_tolerance_days</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>As-of date of the roll. Every window is measured from here.</t>
+          <t>How far lease start may sit from move-in before a lease stops counting as a new tenant. A knob on the output, not a constant buried in code.</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
         <is>
-          <t>Rent roll export</t>
+          <t>Supplied by the operator</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
-          <t>Analysis date</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="5" t="inlineStr">
-        <is>
-          <t>Trade-out</t>
-        </is>
-      </c>
-      <c r="B161" s="5" t="n"/>
-      <c r="C161" s="5" t="n"/>
-      <c r="D161" s="5" t="n"/>
-      <c r="E161" s="5" t="n"/>
-      <c r="F161" s="5" t="n"/>
-      <c r="G161" s="5" t="n"/>
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll — totals</t>
+        </is>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>absent_reason</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D161" s="7" t="inlineStr">
+        <is>
+          <t>Why the rent-roll section is empty, when no roll was supplied. An empty block that says why is a deliverable; a block of zeroes is not.</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F161" s="7" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G161" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
+          <t>Rent roll — totals</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>roll_as_of</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D162" s="7" t="inlineStr">
+        <is>
+          <t>As-of date of the roll. Every window is measured from here.</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll export</t>
+        </is>
+      </c>
+      <c r="F162" s="7" t="inlineStr">
+        <is>
+          <t>Analysis date</t>
+        </is>
+      </c>
+      <c r="G162" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
           <t>Trade-out</t>
         </is>
       </c>
-      <c r="B162" s="6" t="inlineStr">
-        <is>
-          <t>cohort</t>
-        </is>
-      </c>
-      <c r="C162" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D162" s="7" t="inlineStr">
-        <is>
-          <t>New, Renewal, or First generation.</t>
-        </is>
-      </c>
-      <c r="E162" s="6" t="inlineStr">
-        <is>
-          <t>Lease trade-out report</t>
-        </is>
-      </c>
-      <c r="F162" s="7" t="inlineStr">
-        <is>
-          <t>New-vs-renewal growth evidence</t>
-        </is>
-      </c>
-      <c r="G162" s="7" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="6" t="inlineStr">
-        <is>
-          <t>Trade-out</t>
-        </is>
-      </c>
-      <c r="B163" s="6" t="inlineStr">
-        <is>
-          <t>cohort_leases</t>
-        </is>
-      </c>
-      <c r="C163" s="6" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D163" s="7" t="inlineStr">
-        <is>
-          <t>Leases in the cohort.</t>
-        </is>
-      </c>
-      <c r="E163" s="6" t="inlineStr">
-        <is>
-          <t>Lease trade-out report</t>
-        </is>
-      </c>
-      <c r="F163" s="7" t="inlineStr">
-        <is>
-          <t>Sample size</t>
-        </is>
-      </c>
-      <c r="G163" s="7" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+      <c r="B163" s="5" t="n"/>
+      <c r="C163" s="5" t="n"/>
+      <c r="D163" s="5" t="n"/>
+      <c r="E163" s="5" t="n"/>
+      <c r="F163" s="5" t="n"/>
+      <c r="G163" s="5" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
@@ -5900,17 +5900,17 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>cohort_prior_rent</t>
+          <t>cohort</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D164" s="7" t="inlineStr">
         <is>
-          <t>Average rent before the trade.</t>
+          <t>New, Renewal, or First generation.</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="F164" s="7" t="inlineStr">
         <is>
-          <t>Prior rent</t>
+          <t>New-vs-renewal growth evidence</t>
         </is>
       </c>
       <c r="G164" s="7" t="inlineStr">
         <is>
-          <t>$1,706</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -5937,17 +5937,17 @@
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>cohort_new_rent_gross</t>
+          <t>cohort_leases</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>Average new rent before concessions.</t>
+          <t>Leases in the cohort.</t>
         </is>
       </c>
       <c r="E165" s="6" t="inlineStr">
@@ -5957,12 +5957,12 @@
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
-          <t>Gross trade-out</t>
+          <t>Sample size</t>
         </is>
       </c>
       <c r="G165" s="7" t="inlineStr">
         <is>
-          <t>$1,812</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>cohort_new_rent_effective</t>
+          <t>cohort_prior_rent</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="D166" s="7" t="inlineStr">
         <is>
-          <t>Average new rent after concessions. Quoted separately from gross, because quoting one as the other is how a trade-out number becomes wrong.</t>
+          <t>Average rent before the trade.</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
@@ -5994,12 +5994,12 @@
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>Effective trade-out</t>
+          <t>Prior rent</t>
         </is>
       </c>
       <c r="G166" s="7" t="inlineStr">
         <is>
-          <t>$1,774</t>
+          <t>$1,706</t>
         </is>
       </c>
     </row>
@@ -6011,32 +6011,32 @@
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>cohort_gross_change_pct</t>
+          <t>cohort_new_rent_gross</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>Gross change over prior rent.</t>
+          <t>Average new rent before concessions.</t>
         </is>
       </c>
       <c r="E167" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Lease trade-out report</t>
         </is>
       </c>
       <c r="F167" s="7" t="inlineStr">
         <is>
-          <t>Rent growth evidence</t>
+          <t>Gross trade-out</t>
         </is>
       </c>
       <c r="G167" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$1,812</t>
         </is>
       </c>
     </row>
@@ -6048,32 +6048,32 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>cohort_effective_change_pct</t>
+          <t>cohort_new_rent_effective</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D168" s="7" t="inlineStr">
         <is>
-          <t>Effective change over prior rent.</t>
+          <t>Average new rent after concessions. Quoted separately from gross, because quoting one as the other is how a trade-out number becomes wrong.</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Lease trade-out report</t>
         </is>
       </c>
       <c r="F168" s="7" t="inlineStr">
         <is>
-          <t>Rent growth evidence</t>
+          <t>Effective trade-out</t>
         </is>
       </c>
       <c r="G168" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$1,774</t>
         </is>
       </c>
     </row>
@@ -6085,17 +6085,17 @@
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>absent_reason</t>
+          <t>cohort_gross_change_pct</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>Why the block is empty, when no trade-out report exists. An empty block that says why is a deliverable; a block of plausible numbers is not.</t>
+          <t>Gross change over prior rent.</t>
         </is>
       </c>
       <c r="E169" s="6" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="F169" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Rent growth evidence</t>
         </is>
       </c>
       <c r="G169" s="7" t="inlineStr">
@@ -6115,91 +6115,91 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="5" t="inlineStr">
-        <is>
-          <t>Comps</t>
-        </is>
-      </c>
-      <c r="B170" s="5" t="n"/>
-      <c r="C170" s="5" t="n"/>
-      <c r="D170" s="5" t="n"/>
-      <c r="E170" s="5" t="n"/>
-      <c r="F170" s="5" t="n"/>
-      <c r="G170" s="5" t="n"/>
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t>Trade-out</t>
+        </is>
+      </c>
+      <c r="B170" s="6" t="inlineStr">
+        <is>
+          <t>cohort_effective_change_pct</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D170" s="7" t="inlineStr">
+        <is>
+          <t>Effective change over prior rent.</t>
+        </is>
+      </c>
+      <c r="E170" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>Rent growth evidence</t>
+        </is>
+      </c>
+      <c r="G170" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
         <is>
+          <t>Trade-out</t>
+        </is>
+      </c>
+      <c r="B171" s="6" t="inlineStr">
+        <is>
+          <t>absent_reason</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>Why the block is empty, when no trade-out report exists. An empty block that says why is a deliverable; a block of plausible numbers is not.</t>
+        </is>
+      </c>
+      <c r="E171" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="inlineStr">
+        <is>
           <t>Comps</t>
         </is>
       </c>
-      <c r="B171" s="6" t="inlineStr">
-        <is>
-          <t>comp_community</t>
-        </is>
-      </c>
-      <c r="C171" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D171" s="7" t="inlineStr">
-        <is>
-          <t>Comparable community name.</t>
-        </is>
-      </c>
-      <c r="E171" s="6" t="inlineStr">
-        <is>
-          <t>Operator's own weekly rent scrape</t>
-        </is>
-      </c>
-      <c r="F171" s="7" t="inlineStr">
-        <is>
-          <t>Comp set</t>
-        </is>
-      </c>
-      <c r="G171" s="7" t="inlineStr">
-        <is>
-          <t>Alderwood Crossing</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="6" t="inlineStr">
-        <is>
-          <t>Comps</t>
-        </is>
-      </c>
-      <c r="B172" s="6" t="inlineStr">
-        <is>
-          <t>comp_distance_mi</t>
-        </is>
-      </c>
-      <c r="C172" s="6" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="D172" s="7" t="inlineStr">
-        <is>
-          <t>Straight-line distance from the subject.</t>
-        </is>
-      </c>
-      <c r="E172" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F172" s="7" t="inlineStr">
-        <is>
-          <t>Comp set</t>
-        </is>
-      </c>
-      <c r="G172" s="7" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
+      <c r="B172" s="5" t="n"/>
+      <c r="C172" s="5" t="n"/>
+      <c r="D172" s="5" t="n"/>
+      <c r="E172" s="5" t="n"/>
+      <c r="F172" s="5" t="n"/>
+      <c r="G172" s="5" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>comp_floor_plan</t>
+          <t>comp_community</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>Comp floor plan the row describes. Comps are stated per plan, not as one blended community number.</t>
+          <t>Comparable community name.</t>
         </is>
       </c>
       <c r="E173" s="6" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="G173" s="7" t="inlineStr">
         <is>
-          <t>1BR-A</t>
+          <t>Alderwood Crossing</t>
         </is>
       </c>
     </row>
@@ -6246,17 +6246,17 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>comp_tier</t>
+          <t>comp_distance_mi</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D174" s="7" t="inlineStr">
         <is>
-          <t>1 = top comps (the closest five matching the subject's product and vintage), 2 = additional comps (the next fifteen). Tier 3 is identity-only and carries no rent.</t>
+          <t>Straight-line distance from the subject.</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G174" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
@@ -6283,17 +6283,17 @@
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>comp_year_built</t>
+          <t>comp_floor_plan</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>Comp vintage where one is published. Blank means nobody published one — the tracker has no year-built column — never that the community is new.</t>
+          <t>Comp floor plan the row describes. Comps are stated per plan, not as one blended community number.</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="G175" s="7" t="inlineStr">
         <is>
-          <t>2,021</t>
+          <t>1BR-A</t>
         </is>
       </c>
     </row>
@@ -6320,32 +6320,32 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>comp_year_built_source</t>
+          <t>comp_tier</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D176" s="7" t="inlineStr">
         <is>
-          <t>Where that year came from. Blank alongside a blank year; a year with no source is rejected at validation.</t>
+          <t>1 = top comps (the closest five matching the subject's product and vintage), 2 = additional comps (the next fifteen). Tier 3 is identity-only and carries no rent.</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F176" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G176" s="7" t="inlineStr">
         <is>
-          <t>vendor note on the tracked community record</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6357,17 +6357,17 @@
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>nearby_community</t>
+          <t>comp_year_built</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>A tracked community inside the radius that is NOT a comp.</t>
+          <t>Comp vintage where one is published. Blank means nobody published one — the tracker has no year-built column — never that the community is new.</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
@@ -6377,12 +6377,12 @@
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>Market context</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>Rushmere Townhomes</t>
+          <t>2,021</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>nearby_address</t>
+          <t>comp_year_built_source</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="D178" s="7" t="inlineStr">
         <is>
-          <t>Its address, so the reader can place it.</t>
+          <t>Where that year came from. Blank alongside a blank year; a year with no source is rejected at validation.</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="F178" s="7" t="inlineStr">
         <is>
-          <t>Market context</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G178" s="7" t="inlineStr">
         <is>
-          <t>375 Sample Street, Demo City</t>
+          <t>vendor note on the tracked community record</t>
         </is>
       </c>
     </row>
@@ -6431,22 +6431,22 @@
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>nearby_distance_mi</t>
+          <t>nearby_community</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>Distance from the subject.</t>
+          <t>A tracked community inside the radius that is NOT a comp.</t>
         </is>
       </c>
       <c r="E179" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F179" s="7" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="G179" s="7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>Rushmere Townhomes</t>
         </is>
       </c>
     </row>
@@ -6468,17 +6468,17 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>nearby_units</t>
+          <t>nearby_address</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D180" s="7" t="inlineStr">
         <is>
-          <t>Unit count where the registry has one.</t>
+          <t>Its address, so the reader can place it.</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="G180" s="7" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>375 Sample Street, Demo City</t>
         </is>
       </c>
     </row>
@@ -6505,17 +6505,17 @@
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>nearby_reason</t>
+          <t>nearby_distance_mi</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>Why it is not a comp: wrong product, vintage outside the band, no quoted rent, excluded by the tracker, or simply beyond the closest twenty. The column that answers 'why isn't the property across the street in your comp set?'.</t>
+          <t>Distance from the subject.</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="G181" s="7" t="inlineStr">
         <is>
-          <t>different product: tracked as bfr, subject is MF</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -6542,32 +6542,32 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>compset_vintage_footnote</t>
+          <t>nearby_units</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D182" s="7" t="inlineStr">
         <is>
-          <t>The disclosure on the detailed tiers: the band applied, and whether some communities carried no year and so could not be tested.</t>
+          <t>Unit count where the registry has one.</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F182" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G182" s="7" t="inlineStr">
         <is>
-          <t>Vintage filter applied where year known: +/-10 years of the subject's year built. 1 of 11 communities shown carry no published year and were matched on distance and product only.</t>
+          <t>96</t>
         </is>
       </c>
     </row>
@@ -6579,32 +6579,32 @@
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>comp_beds</t>
+          <t>nearby_reason</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>Bedrooms in the comp plan.</t>
+          <t>Why it is not a comp: wrong product, vintage outside the band, no quoted rent, excluded by the tracker, or simply beyond the closest twenty. The column that answers 'why isn't the property across the street in your comp set?'.</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F183" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G183" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>different product: tracked as bfr, subject is MF</t>
         </is>
       </c>
     </row>
@@ -6616,32 +6616,32 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>comp_baths</t>
+          <t>compset_vintage_footnote</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D184" s="7" t="inlineStr">
         <is>
-          <t>Bathrooms in the comp plan.</t>
+          <t>The disclosure on the detailed tiers: the band applied, and whether some communities carried no year and so could not be tested.</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F184" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G184" s="7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Vintage filter applied where year known: +/-10 years of the subject's year built. 1 of 11 communities shown carry no published year and were matched on distance and product only.</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>comp_sqft</t>
+          <t>comp_beds</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="D185" s="7" t="inlineStr">
         <is>
-          <t>Square footage of the comp plan.</t>
+          <t>Bedrooms in the comp plan.</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="G185" s="7" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6690,17 +6690,17 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>comp_asking_rent</t>
+          <t>comp_baths</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D186" s="7" t="inlineStr">
         <is>
-          <t>Advertised asking rent.</t>
+          <t>Bathrooms in the comp plan.</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="F186" s="7" t="inlineStr">
         <is>
-          <t>Market rent evidence</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G186" s="7" t="inlineStr">
         <is>
-          <t>$1,450</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -6727,17 +6727,17 @@
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>comp_concession</t>
+          <t>comp_sqft</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D187" s="7" t="inlineStr">
         <is>
-          <t>Monthly value of the advertised concession.</t>
+          <t>Square footage of the comp plan.</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
@@ -6747,12 +6747,12 @@
       </c>
       <c r="F187" s="7" t="inlineStr">
         <is>
-          <t>Concession assumption</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G187" s="7" t="inlineStr">
         <is>
-          <t>$45</t>
+          <t>735</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>comp_net_effective_rent</t>
+          <t>comp_asking_rent</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="D188" s="7" t="inlineStr">
         <is>
-          <t>Asking rent less the amortized concession. Stated on every row — a concession-blind comp set is the most common way a rent assumption goes wrong.</t>
+          <t>Advertised asking rent.</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F188" s="7" t="inlineStr">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="G188" s="7" t="inlineStr">
         <is>
-          <t>$1,405</t>
+          <t>$1,450</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>comp_asking_psf</t>
+          <t>comp_concession</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
@@ -6811,22 +6811,22 @@
       </c>
       <c r="D189" s="7" t="inlineStr">
         <is>
-          <t>Asking rent per square foot.</t>
+          <t>Monthly value of the advertised concession.</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F189" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Concession assumption</t>
         </is>
       </c>
       <c r="G189" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$45</t>
         </is>
       </c>
     </row>
@@ -6838,32 +6838,32 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>comp_occupancy</t>
+          <t>comp_net_effective_rent</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D190" s="7" t="inlineStr">
         <is>
-          <t>Occupancy where the source published it.</t>
+          <t>Asking rent less the amortized concession. Stated on every row — a concession-blind comp set is the most common way a rent assumption goes wrong.</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F190" s="7" t="inlineStr">
         <is>
-          <t>Market context</t>
+          <t>Market rent evidence</t>
         </is>
       </c>
       <c r="G190" s="7" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>$1,405</t>
         </is>
       </c>
     </row>
@@ -6875,32 +6875,32 @@
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>comp_as_of</t>
+          <t>comp_asking_psf</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D191" s="7" t="inlineStr">
         <is>
-          <t>When the row was scraped.</t>
+          <t>Asking rent per square foot.</t>
         </is>
       </c>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F191" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G191" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6912,17 +6912,17 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>comp_source</t>
+          <t>comp_occupancy</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D192" s="7" t="inlineStr">
         <is>
-          <t>Always the operator's own weekly scrape. Licensed comp feeds are excluded by design and cannot be represented in this schema.</t>
+          <t>Occupancy where the source published it.</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="F192" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G192" s="7" t="inlineStr">
         <is>
-          <t>own weekly scrape</t>
+          <t>94.0%</t>
         </is>
       </c>
     </row>
@@ -6949,32 +6949,32 @@
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>compset_avg_asking</t>
+          <t>comp_as_of</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D193" s="7" t="inlineStr">
         <is>
-          <t>Average asking rent across the comp set.</t>
+          <t>When the row was scraped.</t>
         </is>
       </c>
       <c r="E193" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F193" s="7" t="inlineStr">
         <is>
-          <t>Market rent benchmark</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G193" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
@@ -6986,32 +6986,32 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>compset_avg_net_effective</t>
+          <t>comp_source</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D194" s="7" t="inlineStr">
         <is>
-          <t>Average net effective rent across the comp set.</t>
+          <t>Always the operator's own weekly scrape. Licensed comp feeds are excluded by design and cannot be represented in this schema.</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F194" s="7" t="inlineStr">
         <is>
-          <t>Market rent benchmark</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G194" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>own weekly scrape</t>
         </is>
       </c>
     </row>
@@ -7023,17 +7023,17 @@
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>subject_vs_compset_spread</t>
+          <t>compset_avg_asking</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D195" s="7" t="inlineStr">
         <is>
-          <t>Subject market rent over comp-set net effective, less one.</t>
+          <t>Average asking rent across the comp set.</t>
         </is>
       </c>
       <c r="E195" s="6" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="F195" s="7" t="inlineStr">
         <is>
-          <t>Rent positioning</t>
+          <t>Market rent benchmark</t>
         </is>
       </c>
       <c r="G195" s="7" t="inlineStr">
@@ -7053,91 +7053,91 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="5" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="B196" s="5" t="n"/>
-      <c r="C196" s="5" t="n"/>
-      <c r="D196" s="5" t="n"/>
-      <c r="E196" s="5" t="n"/>
-      <c r="F196" s="5" t="n"/>
-      <c r="G196" s="5" t="n"/>
+      <c r="A196" s="6" t="inlineStr">
+        <is>
+          <t>Comps</t>
+        </is>
+      </c>
+      <c r="B196" s="6" t="inlineStr">
+        <is>
+          <t>compset_avg_net_effective</t>
+        </is>
+      </c>
+      <c r="C196" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D196" s="7" t="inlineStr">
+        <is>
+          <t>Average net effective rent across the comp set.</t>
+        </is>
+      </c>
+      <c r="E196" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F196" s="7" t="inlineStr">
+        <is>
+          <t>Market rent benchmark</t>
+        </is>
+      </c>
+      <c r="G196" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
         <is>
+          <t>Comps</t>
+        </is>
+      </c>
+      <c r="B197" s="6" t="inlineStr">
+        <is>
+          <t>subject_vs_compset_spread</t>
+        </is>
+      </c>
+      <c r="C197" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D197" s="7" t="inlineStr">
+        <is>
+          <t>Subject market rent over comp-set net effective, less one.</t>
+        </is>
+      </c>
+      <c r="E197" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F197" s="7" t="inlineStr">
+        <is>
+          <t>Rent positioning</t>
+        </is>
+      </c>
+      <c r="G197" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="inlineStr">
+        <is>
           <t>Demand</t>
         </is>
       </c>
-      <c r="B197" s="6" t="inlineStr">
-        <is>
-          <t>demand_ring</t>
-        </is>
-      </c>
-      <c r="C197" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D197" s="7" t="inlineStr">
-        <is>
-          <t>Drive-ring the row describes: 1, 3, 5, or 10 miles, or the MSA.</t>
-        </is>
-      </c>
-      <c r="E197" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F197" s="7" t="inlineStr">
-        <is>
-          <t>Market summary</t>
-        </is>
-      </c>
-      <c r="G197" s="7" t="inlineStr">
-        <is>
-          <t>1 mi</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="6" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="B198" s="6" t="inlineStr">
-        <is>
-          <t>demand_population</t>
-        </is>
-      </c>
-      <c r="C198" s="6" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D198" s="7" t="inlineStr">
-        <is>
-          <t>Population in the ring.</t>
-        </is>
-      </c>
-      <c r="E198" s="6" t="inlineStr">
-        <is>
-          <t>Public demographic data</t>
-        </is>
-      </c>
-      <c r="F198" s="7" t="inlineStr">
-        <is>
-          <t>Market summary</t>
-        </is>
-      </c>
-      <c r="G198" s="7" t="inlineStr">
-        <is>
-          <t>9,840</t>
-        </is>
-      </c>
+      <c r="B198" s="5" t="n"/>
+      <c r="C198" s="5" t="n"/>
+      <c r="D198" s="5" t="n"/>
+      <c r="E198" s="5" t="n"/>
+      <c r="F198" s="5" t="n"/>
+      <c r="G198" s="5" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
@@ -7147,22 +7147,22 @@
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>demand_households</t>
+          <t>demand_ring</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D199" s="7" t="inlineStr">
         <is>
-          <t>Households in the ring.</t>
+          <t>Drive-ring the row describes: 1, 3, 5, or 10 miles, or the MSA.</t>
         </is>
       </c>
       <c r="E199" s="6" t="inlineStr">
         <is>
-          <t>Public demographic data</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F199" s="7" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="G199" s="7" t="inlineStr">
         <is>
-          <t>4,020</t>
+          <t>1 mi</t>
         </is>
       </c>
     </row>
@@ -7184,17 +7184,17 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>demand_median_income</t>
+          <t>demand_population</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D200" s="7" t="inlineStr">
         <is>
-          <t>Median household income in the ring.</t>
+          <t>Population in the ring.</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
@@ -7204,12 +7204,12 @@
       </c>
       <c r="F200" s="7" t="inlineStr">
         <is>
-          <t>Affordability check</t>
+          <t>Market summary</t>
         </is>
       </c>
       <c r="G200" s="7" t="inlineStr">
         <is>
-          <t>$78,400</t>
+          <t>9,840</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>demand_jobs</t>
+          <t>demand_households</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D201" s="7" t="inlineStr">
         <is>
-          <t>Jobs located in the ring.</t>
+          <t>Households in the ring.</t>
         </is>
       </c>
       <c r="E201" s="6" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="G201" s="7" t="inlineStr">
         <is>
-          <t>3,150</t>
+          <t>4,020</t>
         </is>
       </c>
     </row>
@@ -7258,17 +7258,17 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>demand_pop_growth_5yr</t>
+          <t>demand_median_income</t>
         </is>
       </c>
       <c r="C202" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D202" s="7" t="inlineStr">
         <is>
-          <t>Five-year population growth in the ring.</t>
+          <t>Median household income in the ring.</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
@@ -7278,12 +7278,12 @@
       </c>
       <c r="F202" s="7" t="inlineStr">
         <is>
-          <t>Growth assumption evidence</t>
+          <t>Affordability check</t>
         </is>
       </c>
       <c r="G202" s="7" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>$78,400</t>
         </is>
       </c>
     </row>
@@ -7295,121 +7295,121 @@
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>demand_renter_share</t>
+          <t>demand_jobs</t>
         </is>
       </c>
       <c r="C203" s="6" t="inlineStr">
         <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D203" s="7" t="inlineStr">
+        <is>
+          <t>Jobs located in the ring.</t>
+        </is>
+      </c>
+      <c r="E203" s="6" t="inlineStr">
+        <is>
+          <t>Public demographic data</t>
+        </is>
+      </c>
+      <c r="F203" s="7" t="inlineStr">
+        <is>
+          <t>Market summary</t>
+        </is>
+      </c>
+      <c r="G203" s="7" t="inlineStr">
+        <is>
+          <t>3,150</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="6" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B204" s="6" t="inlineStr">
+        <is>
+          <t>demand_pop_growth_5yr</t>
+        </is>
+      </c>
+      <c r="C204" s="6" t="inlineStr">
+        <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="D203" s="7" t="inlineStr">
-        <is>
-          <t>Share of ring households that rent.</t>
-        </is>
-      </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="D204" s="7" t="inlineStr">
+        <is>
+          <t>Five-year population growth in the ring.</t>
+        </is>
+      </c>
+      <c r="E204" s="6" t="inlineStr">
         <is>
           <t>Public demographic data</t>
         </is>
       </c>
-      <c r="F203" s="7" t="inlineStr">
-        <is>
-          <t>Demand context</t>
-        </is>
-      </c>
-      <c r="G203" s="7" t="inlineStr">
-        <is>
-          <t>44.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="5" t="inlineStr">
-        <is>
-          <t>Supply</t>
-        </is>
-      </c>
-      <c r="B204" s="5" t="n"/>
-      <c r="C204" s="5" t="n"/>
-      <c r="D204" s="5" t="n"/>
-      <c r="E204" s="5" t="n"/>
-      <c r="F204" s="5" t="n"/>
-      <c r="G204" s="5" t="n"/>
+      <c r="F204" s="7" t="inlineStr">
+        <is>
+          <t>Growth assumption evidence</t>
+        </is>
+      </c>
+      <c r="G204" s="7" t="inlineStr">
+        <is>
+          <t>6.1%</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
         <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B205" s="6" t="inlineStr">
+        <is>
+          <t>demand_renter_share</t>
+        </is>
+      </c>
+      <c r="C205" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D205" s="7" t="inlineStr">
+        <is>
+          <t>Share of ring households that rent.</t>
+        </is>
+      </c>
+      <c r="E205" s="6" t="inlineStr">
+        <is>
+          <t>Public demographic data</t>
+        </is>
+      </c>
+      <c r="F205" s="7" t="inlineStr">
+        <is>
+          <t>Demand context</t>
+        </is>
+      </c>
+      <c r="G205" s="7" t="inlineStr">
+        <is>
+          <t>44.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="inlineStr">
+        <is>
           <t>Supply</t>
         </is>
       </c>
-      <c r="B205" s="6" t="inlineStr">
-        <is>
-          <t>supply_ring</t>
-        </is>
-      </c>
-      <c r="C205" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D205" s="7" t="inlineStr">
-        <is>
-          <t>Ring the supply row describes.</t>
-        </is>
-      </c>
-      <c r="E205" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F205" s="7" t="inlineStr">
-        <is>
-          <t>Competing supply</t>
-        </is>
-      </c>
-      <c r="G205" s="7" t="inlineStr">
-        <is>
-          <t>1 mi</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="6" t="inlineStr">
-        <is>
-          <t>Supply</t>
-        </is>
-      </c>
-      <c r="B206" s="6" t="inlineStr">
-        <is>
-          <t>supply_stage</t>
-        </is>
-      </c>
-      <c r="C206" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D206" s="7" t="inlineStr">
-        <is>
-          <t>Entitlement, permitted, under construction, or delivered in the last 24 months. Stage is stated because entitled units and delivered units are not the same risk.</t>
-        </is>
-      </c>
-      <c r="E206" s="6" t="inlineStr">
-        <is>
-          <t>Public permit / entitlement records</t>
-        </is>
-      </c>
-      <c r="F206" s="7" t="inlineStr">
-        <is>
-          <t>Competing supply</t>
-        </is>
-      </c>
-      <c r="G206" s="7" t="inlineStr">
-        <is>
-          <t>Entitlement</t>
-        </is>
-      </c>
+      <c r="B206" s="5" t="n"/>
+      <c r="C206" s="5" t="n"/>
+      <c r="D206" s="5" t="n"/>
+      <c r="E206" s="5" t="n"/>
+      <c r="F206" s="5" t="n"/>
+      <c r="G206" s="5" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
@@ -7419,22 +7419,22 @@
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>supply_projects</t>
+          <t>supply_ring</t>
         </is>
       </c>
       <c r="C207" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D207" s="7" t="inlineStr">
         <is>
-          <t>Projects at that ring and stage.</t>
+          <t>Ring the supply row describes.</t>
         </is>
       </c>
       <c r="E207" s="6" t="inlineStr">
         <is>
-          <t>Public permit / entitlement records</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F207" s="7" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="G207" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 mi</t>
         </is>
       </c>
     </row>
@@ -7456,17 +7456,17 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>supply_units</t>
+          <t>supply_stage</t>
         </is>
       </c>
       <c r="C208" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D208" s="7" t="inlineStr">
         <is>
-          <t>Units at that ring and stage.</t>
+          <t>Entitlement, permitted, under construction, or delivered in the last 24 months. Stage is stated because entitled units and delivered units are not the same risk.</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="F208" s="7" t="inlineStr">
         <is>
-          <t>Competing supply / absorption</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G208" s="7" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>supply_ring_total_units</t>
+          <t>supply_projects</t>
         </is>
       </c>
       <c r="C209" s="6" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="D209" s="7" t="inlineStr">
         <is>
-          <t>All pipeline units in the ring across stages.</t>
+          <t>Projects at that ring and stage.</t>
         </is>
       </c>
       <c r="E209" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Public permit / entitlement records</t>
         </is>
       </c>
       <c r="F209" s="7" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="G209" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7530,30 +7530,104 @@
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
+          <t>supply_units</t>
+        </is>
+      </c>
+      <c r="C210" s="6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D210" s="7" t="inlineStr">
+        <is>
+          <t>Units at that ring and stage.</t>
+        </is>
+      </c>
+      <c r="E210" s="6" t="inlineStr">
+        <is>
+          <t>Public permit / entitlement records</t>
+        </is>
+      </c>
+      <c r="F210" s="7" t="inlineStr">
+        <is>
+          <t>Competing supply / absorption</t>
+        </is>
+      </c>
+      <c r="G210" s="7" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="6" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
+        <is>
+          <t>supply_ring_total_units</t>
+        </is>
+      </c>
+      <c r="C211" s="6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D211" s="7" t="inlineStr">
+        <is>
+          <t>All pipeline units in the ring across stages.</t>
+        </is>
+      </c>
+      <c r="E211" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F211" s="7" t="inlineStr">
+        <is>
+          <t>Competing supply</t>
+        </is>
+      </c>
+      <c r="G211" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
+        <is>
           <t>supply_pct_of_ring_stock</t>
         </is>
       </c>
-      <c r="C210" s="6" t="inlineStr">
+      <c r="C212" s="6" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="D210" s="7" t="inlineStr">
+      <c r="D212" s="7" t="inlineStr">
         <is>
           <t>Pipeline units as a share of the ring's existing stock, where stock is known.</t>
         </is>
       </c>
-      <c r="E210" s="6" t="inlineStr">
+      <c r="E212" s="6" t="inlineStr">
         <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="F210" s="7" t="inlineStr">
+      <c r="F212" s="7" t="inlineStr">
         <is>
           <t>Supply pressure</t>
         </is>
       </c>
-      <c r="G210" s="7" t="inlineStr">
+      <c r="G212" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
